--- a/backend/data/EEM.xlsx
+++ b/backend/data/EEM.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.71499252319336</v>
+        <v>32.71499633789062</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.84661865234375</v>
+        <v>33.84661483764648</v>
       </c>
     </row>
     <row r="6">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.57834625244141</v>
+        <v>34.57833862304688</v>
       </c>
     </row>
     <row r="8">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34.82509231567383</v>
+        <v>34.8250846862793</v>
       </c>
     </row>
     <row r="9">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.65492248535156</v>
+        <v>34.6549186706543</v>
       </c>
     </row>
     <row r="10">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34.36563873291016</v>
+        <v>34.36563110351562</v>
       </c>
     </row>
     <row r="11">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34.60386276245117</v>
+        <v>34.60386657714844</v>
       </c>
     </row>
     <row r="12">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35.18244171142578</v>
+        <v>35.18244934082031</v>
       </c>
     </row>
     <row r="14">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>35.35261535644531</v>
+        <v>35.35261917114258</v>
       </c>
     </row>
     <row r="15">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34.7400016784668</v>
+        <v>34.74000549316406</v>
       </c>
     </row>
     <row r="16">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>35.09736251831055</v>
+        <v>35.09735488891602</v>
       </c>
     </row>
     <row r="17">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>35.90567016601562</v>
+        <v>35.90566253662109</v>
       </c>
     </row>
     <row r="19">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>35.59085464477539</v>
+        <v>35.59085083007812</v>
       </c>
     </row>
     <row r="21">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>36.36511611938477</v>
+        <v>36.36511993408203</v>
       </c>
     </row>
     <row r="22">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>36.38213729858398</v>
+        <v>36.38213348388672</v>
       </c>
     </row>
     <row r="24">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>36.44169616699219</v>
+        <v>36.44168853759766</v>
       </c>
     </row>
     <row r="25">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>36.44169616699219</v>
+        <v>36.44168853759766</v>
       </c>
     </row>
     <row r="27">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>36.07583236694336</v>
+        <v>36.07583618164062</v>
       </c>
     </row>
     <row r="28">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>35.87162780761719</v>
+        <v>35.87162399291992</v>
       </c>
     </row>
     <row r="29">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>35.75251388549805</v>
+        <v>35.75251770019531</v>
       </c>
     </row>
     <row r="30">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>35.86311721801758</v>
+        <v>35.86312103271484</v>
       </c>
     </row>
     <row r="33">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>35.81206893920898</v>
+        <v>35.81207275390625</v>
       </c>
     </row>
     <row r="34">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>36.09285354614258</v>
+        <v>36.09284591674805</v>
       </c>
     </row>
     <row r="35">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>36.22047805786133</v>
+        <v>36.2204704284668</v>
       </c>
     </row>
     <row r="37">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>36.62037658691406</v>
+        <v>36.6203727722168</v>
       </c>
     </row>
     <row r="38">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>37.02877807617188</v>
+        <v>37.02877426147461</v>
       </c>
     </row>
     <row r="39">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>36.90115356445312</v>
+        <v>36.90114593505859</v>
       </c>
     </row>
     <row r="40">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>36.58634948730469</v>
+        <v>36.58633422851562</v>
       </c>
     </row>
     <row r="41">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>36.10986328125</v>
+        <v>36.10985946655273</v>
       </c>
     </row>
     <row r="42">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>36.15240478515625</v>
+        <v>36.15241241455078</v>
       </c>
     </row>
     <row r="43">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>36.20345687866211</v>
+        <v>36.20346069335938</v>
       </c>
     </row>
     <row r="44">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>36.56081771850586</v>
+        <v>36.56082153320312</v>
       </c>
     </row>
     <row r="45">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>36.35660552978516</v>
+        <v>36.35660934448242</v>
       </c>
     </row>
     <row r="46">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>35.6844482421875</v>
+        <v>35.68444061279297</v>
       </c>
     </row>
     <row r="47">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>35.42919158935547</v>
+        <v>35.42918014526367</v>
       </c>
     </row>
     <row r="48">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>36.09285354614258</v>
+        <v>36.09284591674805</v>
       </c>
     </row>
     <row r="49">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>36.280029296875</v>
+        <v>36.28003692626953</v>
       </c>
     </row>
     <row r="50">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>36.32257461547852</v>
+        <v>36.32257080078125</v>
       </c>
     </row>
     <row r="51">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>36.12687683105469</v>
+        <v>36.12688064575195</v>
       </c>
     </row>
     <row r="52">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>36.6544075012207</v>
+        <v>36.65440368652344</v>
       </c>
     </row>
     <row r="53">
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>37.06280517578125</v>
+        <v>37.06281280517578</v>
       </c>
     </row>
     <row r="54">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>37.07982635498047</v>
+        <v>37.07983779907227</v>
       </c>
     </row>
     <row r="55">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>37.1904411315918</v>
+        <v>37.19043350219727</v>
       </c>
     </row>
     <row r="57">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>36.10135650634766</v>
+        <v>36.10136032104492</v>
       </c>
     </row>
     <row r="58">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>35.90567016601562</v>
+        <v>35.90566253662109</v>
       </c>
     </row>
     <row r="61">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>36.14389801025391</v>
+        <v>36.14389038085938</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>36.51826858520508</v>
+        <v>36.51826095581055</v>
       </c>
     </row>
     <row r="63">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>37.12237167358398</v>
+        <v>37.12237548828125</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>37.00325393676758</v>
+        <v>37.00325012207031</v>
       </c>
     </row>
     <row r="65">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>37.25849914550781</v>
+        <v>37.25851058959961</v>
       </c>
     </row>
     <row r="66">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>37.48823928833008</v>
+        <v>37.48823547363281</v>
       </c>
     </row>
     <row r="67">
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>37.77751922607422</v>
+        <v>37.77752304077148</v>
       </c>
     </row>
     <row r="68">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>37.77751922607422</v>
+        <v>37.77752304077148</v>
       </c>
     </row>
     <row r="69">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>37.70095443725586</v>
+        <v>37.70094299316406</v>
       </c>
     </row>
     <row r="70">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>37.74348449707031</v>
+        <v>37.74349975585938</v>
       </c>
     </row>
     <row r="73">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>37.54779052734375</v>
+        <v>37.54779815673828</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>37.93918228149414</v>
+        <v>37.93917846679688</v>
       </c>
     </row>
     <row r="76">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>37.91365814208984</v>
+        <v>37.91366577148438</v>
       </c>
     </row>
     <row r="77">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>37.66690444946289</v>
+        <v>37.66691207885742</v>
       </c>
     </row>
     <row r="78">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>37.75199508666992</v>
+        <v>37.75199890136719</v>
       </c>
     </row>
     <row r="79">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>37.24148559570312</v>
+        <v>37.24149322509766</v>
       </c>
     </row>
     <row r="80">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>37.1904411315918</v>
+        <v>37.19043350219727</v>
       </c>
     </row>
     <row r="81">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>37.33508682250977</v>
+        <v>37.33507919311523</v>
       </c>
     </row>
     <row r="82">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>37.09684753417969</v>
+        <v>37.09683990478516</v>
       </c>
     </row>
     <row r="85">
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>37.18192291259766</v>
+        <v>37.18193435668945</v>
       </c>
     </row>
     <row r="86">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>37.62436676025391</v>
+        <v>37.6243782043457</v>
       </c>
     </row>
     <row r="87">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>36.85009765625</v>
+        <v>36.8501091003418</v>
       </c>
     </row>
     <row r="88">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>36.12687683105469</v>
+        <v>36.12688064575195</v>
       </c>
     </row>
     <row r="89">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>36.07583236694336</v>
+        <v>36.07583618164062</v>
       </c>
     </row>
     <row r="90">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>35.50577163696289</v>
+        <v>35.50576782226562</v>
       </c>
     </row>
     <row r="91">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>35.71847534179688</v>
+        <v>35.71847152709961</v>
       </c>
     </row>
     <row r="92">
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>34.52729797363281</v>
+        <v>34.52729034423828</v>
       </c>
     </row>
     <row r="93">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>35.08034896850586</v>
+        <v>35.08034133911133</v>
       </c>
     </row>
     <row r="95">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>34.91017532348633</v>
+        <v>34.91017150878906</v>
       </c>
     </row>
     <row r="96">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>34.28054428100586</v>
+        <v>34.28055191040039</v>
       </c>
     </row>
     <row r="97">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>34.13590621948242</v>
+        <v>34.13589477539062</v>
       </c>
     </row>
     <row r="98">
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>34.39966583251953</v>
+        <v>34.39966201782227</v>
       </c>
     </row>
     <row r="100">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>33.99126434326172</v>
+        <v>33.99125671386719</v>
       </c>
     </row>
     <row r="102">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>34.11038208007812</v>
+        <v>34.11037826538086</v>
       </c>
     </row>
     <row r="103">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>34.51877975463867</v>
+        <v>34.51879119873047</v>
       </c>
     </row>
     <row r="105">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>34.63790130615234</v>
+        <v>34.63789749145508</v>
       </c>
     </row>
     <row r="106">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>34.95272064208984</v>
+        <v>34.95271682739258</v>
       </c>
     </row>
     <row r="107">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>34.74851608276367</v>
+        <v>34.74851989746094</v>
       </c>
     </row>
     <row r="109">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>34.76552963256836</v>
+        <v>34.76553344726562</v>
       </c>
     </row>
     <row r="110">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>35.03780364990234</v>
+        <v>35.03779983520508</v>
       </c>
     </row>
     <row r="111">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>35.80356216430664</v>
+        <v>35.80355834960938</v>
       </c>
     </row>
     <row r="113">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>35.42068862915039</v>
+        <v>35.42068099975586</v>
       </c>
     </row>
     <row r="114">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>35.36112594604492</v>
+        <v>35.36111831665039</v>
       </c>
     </row>
     <row r="115">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>35.10776519775391</v>
+        <v>35.10776901245117</v>
       </c>
     </row>
     <row r="117">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>35.9565315246582</v>
+        <v>35.95652389526367</v>
       </c>
     </row>
     <row r="118">
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>36.78813171386719</v>
+        <v>36.78813934326172</v>
       </c>
     </row>
     <row r="120">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>36.58237075805664</v>
+        <v>36.58237457275391</v>
       </c>
     </row>
     <row r="124">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>36.83957672119141</v>
+        <v>36.83958053588867</v>
       </c>
     </row>
     <row r="125">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>36.78813171386719</v>
+        <v>36.78813934326172</v>
       </c>
     </row>
     <row r="126">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>37.22537612915039</v>
+        <v>37.22536849975586</v>
       </c>
     </row>
     <row r="127">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>37.06248092651367</v>
+        <v>37.06247711181641</v>
       </c>
     </row>
     <row r="129">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>36.8052864074707</v>
+        <v>36.80528259277344</v>
       </c>
     </row>
     <row r="130">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>36.58237075805664</v>
+        <v>36.58237457275391</v>
       </c>
     </row>
     <row r="131">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>36.77956390380859</v>
+        <v>36.77956771850586</v>
       </c>
     </row>
     <row r="133">
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>36.71097946166992</v>
+        <v>36.71097564697266</v>
       </c>
     </row>
     <row r="134">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>36.7366943359375</v>
+        <v>36.7367057800293</v>
       </c>
     </row>
     <row r="135">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>36.87386322021484</v>
+        <v>36.87387466430664</v>
       </c>
     </row>
     <row r="136">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>36.82242584228516</v>
+        <v>36.82242965698242</v>
       </c>
     </row>
     <row r="137">
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>36.71097946166992</v>
+        <v>36.71097564697266</v>
       </c>
     </row>
     <row r="138">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>36.93388366699219</v>
+        <v>36.93387985229492</v>
       </c>
     </row>
     <row r="139">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>36.75384521484375</v>
+        <v>36.75384140014648</v>
       </c>
     </row>
     <row r="141">
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>36.53093338012695</v>
+        <v>36.53093719482422</v>
       </c>
     </row>
     <row r="144">
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>36.53950500488281</v>
+        <v>36.53950119018555</v>
       </c>
     </row>
     <row r="146">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>35.10776519775391</v>
+        <v>35.10776901245117</v>
       </c>
     </row>
     <row r="149">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>33.47882843017578</v>
+        <v>33.47883224487305</v>
       </c>
     </row>
     <row r="151">
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>33.95893859863281</v>
+        <v>33.95893478393555</v>
       </c>
     </row>
     <row r="152">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>34.11325836181641</v>
+        <v>34.11326217651367</v>
       </c>
     </row>
     <row r="153">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>34.53335571289062</v>
+        <v>34.53334808349609</v>
       </c>
     </row>
     <row r="154">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>34.18184661865234</v>
+        <v>34.18184280395508</v>
       </c>
     </row>
     <row r="155">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>33.77032089233398</v>
+        <v>33.77032852172852</v>
       </c>
     </row>
     <row r="156">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>34.19899749755859</v>
+        <v>34.19898986816406</v>
       </c>
     </row>
     <row r="157">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>33.43597030639648</v>
+        <v>33.43596649169922</v>
       </c>
     </row>
     <row r="159">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>34.03609848022461</v>
+        <v>34.03609466552734</v>
       </c>
     </row>
     <row r="161">
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>34.10467529296875</v>
+        <v>34.10468673706055</v>
       </c>
     </row>
     <row r="162">
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>33.98465728759766</v>
+        <v>33.98464965820312</v>
       </c>
     </row>
     <row r="164">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>33.47882843017578</v>
+        <v>33.47883224487305</v>
       </c>
     </row>
     <row r="165">
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>33.7188835144043</v>
+        <v>33.71889495849609</v>
       </c>
     </row>
     <row r="167">
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>33.81319808959961</v>
+        <v>33.81319046020508</v>
       </c>
     </row>
     <row r="168">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>34.1904182434082</v>
+        <v>34.19042205810547</v>
       </c>
     </row>
     <row r="169">
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>34.45619583129883</v>
+        <v>34.45618438720703</v>
       </c>
     </row>
     <row r="170">
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>34.24185562133789</v>
+        <v>34.24186325073242</v>
       </c>
     </row>
     <row r="171">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>34.81627655029297</v>
+        <v>34.8162727355957</v>
       </c>
     </row>
     <row r="172">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>35.21065139770508</v>
+        <v>35.21064376831055</v>
       </c>
     </row>
     <row r="173">
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>35.36496734619141</v>
+        <v>35.36496353149414</v>
       </c>
     </row>
     <row r="174">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>35.50214385986328</v>
+        <v>35.50213623046875</v>
       </c>
     </row>
     <row r="176">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>35.75077056884766</v>
+        <v>35.75075912475586</v>
       </c>
     </row>
     <row r="177">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>36.21372985839844</v>
+        <v>36.21372222900391</v>
       </c>
     </row>
     <row r="179">
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>35.93080520629883</v>
+        <v>35.93080139160156</v>
       </c>
     </row>
     <row r="180">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>35.93080520629883</v>
+        <v>35.93080139160156</v>
       </c>
     </row>
     <row r="181">
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>35.63930892944336</v>
+        <v>35.63931274414062</v>
       </c>
     </row>
     <row r="183">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>35.67360687255859</v>
+        <v>35.67360305786133</v>
       </c>
     </row>
     <row r="184">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>35.70789337158203</v>
+        <v>35.7078971862793</v>
       </c>
     </row>
     <row r="185">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>35.30495834350586</v>
+        <v>35.30495452880859</v>
       </c>
     </row>
     <row r="187">
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>35.29637908935547</v>
+        <v>35.29636764526367</v>
       </c>
     </row>
     <row r="188">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>34.84199142456055</v>
+        <v>34.84198760986328</v>
       </c>
     </row>
     <row r="189">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>35.03918075561523</v>
+        <v>35.0391731262207</v>
       </c>
     </row>
     <row r="190">
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>34.79055404663086</v>
+        <v>34.79055023193359</v>
       </c>
     </row>
     <row r="191">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>34.5247802734375</v>
+        <v>34.52478790283203</v>
       </c>
     </row>
     <row r="192">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>34.97060394287109</v>
+        <v>34.97058868408203</v>
       </c>
     </row>
     <row r="193">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>34.58479309082031</v>
+        <v>34.58479690551758</v>
       </c>
     </row>
     <row r="196">
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>34.85055923461914</v>
+        <v>34.85056304931641</v>
       </c>
     </row>
     <row r="197">
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>35.21065139770508</v>
+        <v>35.21064376831055</v>
       </c>
     </row>
     <row r="198">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>35.7764892578125</v>
+        <v>35.7764778137207</v>
       </c>
     </row>
     <row r="199">
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>35.62216567993164</v>
+        <v>35.62216949462891</v>
       </c>
     </row>
     <row r="200">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>35.93937683105469</v>
+        <v>35.93938446044922</v>
       </c>
     </row>
     <row r="201">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>36.04225540161133</v>
+        <v>36.04225158691406</v>
       </c>
     </row>
     <row r="202">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>36.17943572998047</v>
+        <v>36.1794319152832</v>
       </c>
     </row>
     <row r="203">
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>35.99081420898438</v>
+        <v>35.99081039428711</v>
       </c>
     </row>
     <row r="204">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>36.31660079956055</v>
+        <v>36.31660842895508</v>
       </c>
     </row>
     <row r="205">
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>36.34233093261719</v>
+        <v>36.34232711791992</v>
       </c>
     </row>
     <row r="206">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>36.35089111328125</v>
+        <v>36.35090255737305</v>
       </c>
     </row>
     <row r="207">
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>36.35089111328125</v>
+        <v>36.35090255737305</v>
       </c>
     </row>
     <row r="208">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>36.82242584228516</v>
+        <v>36.82242965698242</v>
       </c>
     </row>
     <row r="210">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>36.63381195068359</v>
+        <v>36.63381958007812</v>
       </c>
     </row>
     <row r="211">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>36.50521087646484</v>
+        <v>36.50521469116211</v>
       </c>
     </row>
     <row r="213">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>37.05390930175781</v>
+        <v>37.05391311645508</v>
       </c>
     </row>
     <row r="214">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>37.42256546020508</v>
+        <v>37.42256927490234</v>
       </c>
     </row>
     <row r="215">
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>37.63689422607422</v>
+        <v>37.63689804077148</v>
       </c>
     </row>
     <row r="216">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>37.51686859130859</v>
+        <v>37.51687240600586</v>
       </c>
     </row>
     <row r="217">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>37.44828414916992</v>
+        <v>37.44828033447266</v>
       </c>
     </row>
     <row r="219">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>37.18251419067383</v>
+        <v>37.18251800537109</v>
       </c>
     </row>
     <row r="220">
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>36.94245147705078</v>
+        <v>36.94245529174805</v>
       </c>
     </row>
     <row r="221">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>36.68525314331055</v>
+        <v>36.68525695800781</v>
       </c>
     </row>
     <row r="223">
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>36.97674942016602</v>
+        <v>36.97674560546875</v>
       </c>
     </row>
     <row r="224">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>36.99389266967773</v>
+        <v>36.993896484375</v>
       </c>
     </row>
     <row r="226">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>36.83100891113281</v>
+        <v>36.83099746704102</v>
       </c>
     </row>
     <row r="227">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>36.75384521484375</v>
+        <v>36.75384140014648</v>
       </c>
     </row>
     <row r="228">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>36.75384521484375</v>
+        <v>36.75384140014648</v>
       </c>
     </row>
     <row r="229">
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>37.01103591918945</v>
+        <v>37.01103973388672</v>
       </c>
     </row>
     <row r="231">
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>37.05390930175781</v>
+        <v>37.05391311645508</v>
       </c>
     </row>
     <row r="232">
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>36.46234512329102</v>
+        <v>36.46234893798828</v>
       </c>
     </row>
     <row r="234">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>36.27374267578125</v>
+        <v>36.27373886108398</v>
       </c>
     </row>
     <row r="235">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>36.54808044433594</v>
+        <v>36.54808807373047</v>
       </c>
     </row>
     <row r="236">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>36.71097946166992</v>
+        <v>36.71097564697266</v>
       </c>
     </row>
     <row r="237">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>36.9253044128418</v>
+        <v>36.92531204223633</v>
       </c>
     </row>
     <row r="238">
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>36.77956390380859</v>
+        <v>36.77956771850586</v>
       </c>
     </row>
     <row r="239">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>36.90815734863281</v>
+        <v>36.90816116333008</v>
       </c>
     </row>
     <row r="240">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>37.44828414916992</v>
+        <v>37.44828033447266</v>
       </c>
     </row>
     <row r="241">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>38.099853515625</v>
+        <v>38.09985733032227</v>
       </c>
     </row>
     <row r="242">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>38.08270263671875</v>
+        <v>38.08270645141602</v>
       </c>
     </row>
     <row r="243">
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>38.40582656860352</v>
+        <v>38.40581893920898</v>
       </c>
     </row>
     <row r="244">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>38.75608444213867</v>
+        <v>38.75607681274414</v>
       </c>
     </row>
     <row r="245">
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>38.96622848510742</v>
+        <v>38.96623611450195</v>
       </c>
     </row>
     <row r="246">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>38.98374557495117</v>
+        <v>38.98374938964844</v>
       </c>
     </row>
     <row r="247">
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>39.06255340576172</v>
+        <v>39.06254959106445</v>
       </c>
     </row>
     <row r="248">
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>39.30773162841797</v>
+        <v>39.3077392578125</v>
       </c>
     </row>
     <row r="251">
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>39.20265197753906</v>
+        <v>39.20265960693359</v>
       </c>
     </row>
     <row r="253">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>39.29022979736328</v>
+        <v>39.29021835327148</v>
       </c>
     </row>
     <row r="254">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>40.08706283569336</v>
+        <v>40.08705902099609</v>
       </c>
     </row>
     <row r="255">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>39.3427619934082</v>
+        <v>39.34276580810547</v>
       </c>
     </row>
     <row r="256">
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>39.22017288208008</v>
+        <v>39.22016525268555</v>
       </c>
     </row>
     <row r="258">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>39.44784164428711</v>
+        <v>39.44783401489258</v>
       </c>
     </row>
     <row r="259">
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>39.92068481445312</v>
+        <v>39.92068862915039</v>
       </c>
     </row>
     <row r="261">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>40.54238891601562</v>
+        <v>40.54239654541016</v>
       </c>
     </row>
     <row r="262">
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>40.31472778320312</v>
+        <v>40.31473159790039</v>
       </c>
     </row>
     <row r="263">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>39.99949264526367</v>
+        <v>39.9995002746582</v>
       </c>
     </row>
     <row r="264">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>40.25343704223633</v>
+        <v>40.25343322753906</v>
       </c>
     </row>
     <row r="265">
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>40.48109817504883</v>
+        <v>40.48109436035156</v>
       </c>
     </row>
     <row r="266">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>39.45659255981445</v>
+        <v>39.45660400390625</v>
       </c>
     </row>
     <row r="267">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>39.78058624267578</v>
+        <v>39.78059005737305</v>
       </c>
     </row>
     <row r="268">
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>39.36903762817383</v>
+        <v>39.36902618408203</v>
       </c>
     </row>
     <row r="269">
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>39.05379104614258</v>
+        <v>39.05379486083984</v>
       </c>
     </row>
     <row r="270">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>37.70530319213867</v>
+        <v>37.70530700683594</v>
       </c>
     </row>
     <row r="271">
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>38.02053833007812</v>
+        <v>38.02053451538086</v>
       </c>
     </row>
     <row r="272">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>38.20442581176758</v>
+        <v>38.20442199707031</v>
       </c>
     </row>
     <row r="273">
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>37.63524627685547</v>
+        <v>37.63525009155273</v>
       </c>
     </row>
     <row r="274">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>38.24820327758789</v>
+        <v>38.24820709228516</v>
       </c>
     </row>
     <row r="277">
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>38.50214385986328</v>
+        <v>38.50214767456055</v>
       </c>
     </row>
     <row r="279">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>37.96799468994141</v>
+        <v>37.96799850463867</v>
       </c>
     </row>
     <row r="280">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>38.67727279663086</v>
+        <v>38.67726898193359</v>
       </c>
     </row>
     <row r="282">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>39.20265197753906</v>
+        <v>39.20265960693359</v>
       </c>
     </row>
     <row r="283">
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>38.68602752685547</v>
+        <v>38.68603134155273</v>
       </c>
     </row>
     <row r="284">
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>38.70354461669922</v>
+        <v>38.70353698730469</v>
       </c>
     </row>
     <row r="285">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>38.4495964050293</v>
+        <v>38.44960021972656</v>
       </c>
     </row>
     <row r="286">
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>38.72980499267578</v>
+        <v>38.72980880737305</v>
       </c>
     </row>
     <row r="287">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>38.12561416625977</v>
+        <v>38.12561798095703</v>
       </c>
     </row>
     <row r="288">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>37.90670394897461</v>
+        <v>37.90670776367188</v>
       </c>
     </row>
     <row r="289">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>36.19920349121094</v>
+        <v>36.19919967651367</v>
       </c>
     </row>
     <row r="291">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>35.61251449584961</v>
+        <v>35.61250686645508</v>
       </c>
     </row>
     <row r="293">
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>35.48115921020508</v>
+        <v>35.48116683959961</v>
       </c>
     </row>
     <row r="294">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>36.25172805786133</v>
+        <v>36.25173950195312</v>
       </c>
     </row>
     <row r="295">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>36.00654983520508</v>
+        <v>36.00655364990234</v>
       </c>
     </row>
     <row r="296">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>36.64577102661133</v>
+        <v>36.64576721191406</v>
       </c>
     </row>
     <row r="297">
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>35.87520980834961</v>
+        <v>35.87521362304688</v>
       </c>
     </row>
     <row r="298">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>35.1396598815918</v>
+        <v>35.13966369628906</v>
       </c>
     </row>
     <row r="299">
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>32.74038696289062</v>
+        <v>32.74039077758789</v>
       </c>
     </row>
     <row r="300">
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>34.40412139892578</v>
+        <v>34.40412902832031</v>
       </c>
     </row>
     <row r="301">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>29.51801300048828</v>
+        <v>29.51801490783691</v>
       </c>
     </row>
     <row r="303">
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>31.64583969116211</v>
+        <v>31.64583587646484</v>
       </c>
     </row>
     <row r="304">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>29.60558319091797</v>
+        <v>29.6055850982666</v>
       </c>
     </row>
     <row r="306">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>27.04869842529297</v>
+        <v>27.04869651794434</v>
       </c>
     </row>
     <row r="307">
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>27.46025276184082</v>
+        <v>27.46025085449219</v>
       </c>
     </row>
     <row r="309">
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>29.8332462310791</v>
+        <v>29.83324813842773</v>
       </c>
     </row>
     <row r="312">
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>29.20278739929199</v>
+        <v>29.20278167724609</v>
       </c>
     </row>
     <row r="314">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>29.68439292907715</v>
+        <v>29.68439483642578</v>
       </c>
     </row>
     <row r="315">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>29.01013946533203</v>
+        <v>29.01014518737793</v>
       </c>
     </row>
     <row r="319">
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>30.59506225585938</v>
+        <v>30.59506416320801</v>
       </c>
     </row>
     <row r="320">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>30.7526741027832</v>
+        <v>30.75267601013184</v>
       </c>
     </row>
     <row r="321">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>31.06791114807129</v>
+        <v>31.06790924072266</v>
       </c>
     </row>
     <row r="322">
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>30.95408248901367</v>
+        <v>30.95407867431641</v>
       </c>
     </row>
     <row r="323">
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>30.99786186218262</v>
+        <v>30.99785614013672</v>
       </c>
     </row>
     <row r="324">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>31.70712661743164</v>
+        <v>31.70713424682617</v>
       </c>
     </row>
     <row r="325">
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>30.89277839660645</v>
+        <v>30.89278411865234</v>
       </c>
     </row>
     <row r="326">
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>31.05915641784668</v>
+        <v>31.05915832519531</v>
       </c>
     </row>
     <row r="327">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>31.75091361999512</v>
+        <v>31.75091552734375</v>
       </c>
     </row>
     <row r="328">
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>31.34811592102051</v>
+        <v>31.34811210632324</v>
       </c>
     </row>
     <row r="329">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>30.48123359680176</v>
+        <v>30.48122787475586</v>
       </c>
     </row>
     <row r="330">
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>31.19926071166992</v>
+        <v>31.19925308227539</v>
       </c>
     </row>
     <row r="332">
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>31.15547752380371</v>
+        <v>31.15546989440918</v>
       </c>
     </row>
     <row r="333">
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>31.84723281860352</v>
+        <v>31.84722900390625</v>
       </c>
     </row>
     <row r="335">
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>30.92781448364258</v>
+        <v>30.92780303955078</v>
       </c>
     </row>
     <row r="338">
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>31.26054954528809</v>
+        <v>31.26055717468262</v>
       </c>
     </row>
     <row r="339">
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>31.43568229675293</v>
+        <v>31.43568801879883</v>
       </c>
     </row>
     <row r="340">
@@ -3815,7 +3815,7 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>31.3393611907959</v>
+        <v>31.33935928344727</v>
       </c>
     </row>
     <row r="341">
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>31.59329795837402</v>
+        <v>31.59330558776855</v>
       </c>
     </row>
     <row r="342">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>31.9260425567627</v>
+        <v>31.92604637145996</v>
       </c>
     </row>
     <row r="345">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>31.98733901977539</v>
+        <v>31.98734092712402</v>
       </c>
     </row>
     <row r="347">
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>31.54951286315918</v>
+        <v>31.54951858520508</v>
       </c>
     </row>
     <row r="348">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>32.78417205810547</v>
+        <v>32.7841796875</v>
       </c>
     </row>
     <row r="349">
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>32.521484375</v>
+        <v>32.52148818969727</v>
       </c>
     </row>
     <row r="350">
@@ -3915,7 +3915,7 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>32.95055389404297</v>
+        <v>32.95054626464844</v>
       </c>
     </row>
     <row r="351">
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>32.57401657104492</v>
+        <v>32.57402038574219</v>
       </c>
     </row>
     <row r="352">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>31.89977645874023</v>
+        <v>31.89978218078613</v>
       </c>
     </row>
     <row r="353">
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>32.70537567138672</v>
+        <v>32.70536422729492</v>
       </c>
     </row>
     <row r="355">
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>32.47770309448242</v>
+        <v>32.47769546508789</v>
       </c>
     </row>
     <row r="356">
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>33.03811264038086</v>
+        <v>33.03811645507812</v>
       </c>
     </row>
     <row r="357">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>33.79991912841797</v>
+        <v>33.7999267578125</v>
       </c>
     </row>
     <row r="358">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>35.41110992431641</v>
+        <v>35.41111755371094</v>
       </c>
     </row>
     <row r="360">
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>35.83141708374023</v>
+        <v>35.8314208984375</v>
       </c>
     </row>
     <row r="362">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>36.05032730102539</v>
+        <v>36.05033493041992</v>
       </c>
     </row>
     <row r="363">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>35.80515670776367</v>
+        <v>35.80515289306641</v>
       </c>
     </row>
     <row r="364">
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>36.06784820556641</v>
+        <v>36.06784439086914</v>
       </c>
     </row>
     <row r="365">
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>34.18520736694336</v>
+        <v>34.18520355224609</v>
       </c>
     </row>
     <row r="366">
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>34.59492874145508</v>
+        <v>34.59493255615234</v>
       </c>
     </row>
     <row r="368">
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>35.14979934692383</v>
+        <v>35.14979553222656</v>
       </c>
     </row>
     <row r="370">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>35.16740798950195</v>
+        <v>35.16741180419922</v>
       </c>
     </row>
     <row r="371">
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>35.15859985351562</v>
+        <v>35.15859222412109</v>
       </c>
     </row>
     <row r="372">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>35.59015274047852</v>
+        <v>35.59015655517578</v>
       </c>
     </row>
     <row r="373">
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>35.93363571166992</v>
+        <v>35.93363952636719</v>
       </c>
     </row>
     <row r="374">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>35.45804977416992</v>
+        <v>35.45804595947266</v>
       </c>
     </row>
     <row r="375">
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>35.6165771484375</v>
+        <v>35.61658096313477</v>
       </c>
     </row>
     <row r="380">
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>37.99454116821289</v>
+        <v>37.99453735351562</v>
       </c>
     </row>
     <row r="382">
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>38.3292121887207</v>
+        <v>38.32920837402344</v>
       </c>
     </row>
     <row r="384">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>38.3292121887207</v>
+        <v>38.32920837402344</v>
       </c>
     </row>
     <row r="385">
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>38.08261489868164</v>
+        <v>38.08261108398438</v>
       </c>
     </row>
     <row r="386">
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>37.82720565795898</v>
+        <v>37.82719802856445</v>
       </c>
     </row>
     <row r="387">
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>37.88003921508789</v>
+        <v>37.88004302978516</v>
       </c>
     </row>
     <row r="388">
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>37.99454116821289</v>
+        <v>37.99453735351562</v>
       </c>
     </row>
     <row r="389">
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>37.45729446411133</v>
+        <v>37.45729827880859</v>
       </c>
     </row>
     <row r="390">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>37.66867065429688</v>
+        <v>37.66866683959961</v>
       </c>
     </row>
     <row r="391">
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>38.15306854248047</v>
+        <v>38.15307235717773</v>
       </c>
     </row>
     <row r="392">
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>38.50536346435547</v>
+        <v>38.50536727905273</v>
       </c>
     </row>
     <row r="393">
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>37.99454116821289</v>
+        <v>37.99453735351562</v>
       </c>
     </row>
     <row r="396">
@@ -4395,7 +4395,7 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>38.88407135009766</v>
+        <v>38.88407516479492</v>
       </c>
     </row>
     <row r="399">
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>38.12665176391602</v>
+        <v>38.12664794921875</v>
       </c>
     </row>
     <row r="401">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>38.90168762207031</v>
+        <v>38.90168380737305</v>
       </c>
     </row>
     <row r="403">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>39.32444000244141</v>
+        <v>39.32443618774414</v>
       </c>
     </row>
     <row r="404">
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>39.44773864746094</v>
+        <v>39.44773483276367</v>
       </c>
     </row>
     <row r="405">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>38.6374626159668</v>
+        <v>38.63747024536133</v>
       </c>
     </row>
     <row r="406">
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>38.62865829467773</v>
+        <v>38.62865447998047</v>
       </c>
     </row>
     <row r="408">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>39.14829254150391</v>
+        <v>39.14828872680664</v>
       </c>
     </row>
     <row r="409">
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>39.03379058837891</v>
+        <v>39.03379821777344</v>
       </c>
     </row>
     <row r="410">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>38.96334075927734</v>
+        <v>38.96333694458008</v>
       </c>
     </row>
     <row r="411">
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>39.45654296875</v>
+        <v>39.45655059814453</v>
       </c>
     </row>
     <row r="412">
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>39.41250228881836</v>
+        <v>39.41251754760742</v>
       </c>
     </row>
     <row r="413">
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>38.99857330322266</v>
+        <v>38.99856948852539</v>
       </c>
     </row>
     <row r="416">
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>39.43013000488281</v>
+        <v>39.43012237548828</v>
       </c>
     </row>
     <row r="417">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>39.82645034790039</v>
+        <v>39.82645416259766</v>
       </c>
     </row>
     <row r="418">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>39.93213653564453</v>
+        <v>39.93213272094727</v>
       </c>
     </row>
     <row r="419">
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>39.59745788574219</v>
+        <v>39.59746170043945</v>
       </c>
     </row>
     <row r="420">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>40.11708831787109</v>
+        <v>40.11709213256836</v>
       </c>
     </row>
     <row r="421">
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>39.89690017700195</v>
+        <v>39.89690399169922</v>
       </c>
     </row>
     <row r="423">
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>39.79121780395508</v>
+        <v>39.79122161865234</v>
       </c>
     </row>
     <row r="424">
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>39.03379058837891</v>
+        <v>39.03379821777344</v>
       </c>
     </row>
     <row r="425">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>39.05141067504883</v>
+        <v>39.0514030456543</v>
       </c>
     </row>
     <row r="426">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>38.37325286865234</v>
+        <v>38.37326049804688</v>
       </c>
     </row>
     <row r="427">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>38.32040023803711</v>
+        <v>38.32040786743164</v>
       </c>
     </row>
     <row r="429">
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>38.69031524658203</v>
+        <v>38.69031143188477</v>
       </c>
     </row>
     <row r="430">
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>39.31562423706055</v>
+        <v>39.31562805175781</v>
       </c>
     </row>
     <row r="431">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>39.72957229614258</v>
+        <v>39.72956848144531</v>
       </c>
     </row>
     <row r="432">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>39.67673492431641</v>
+        <v>39.67672348022461</v>
       </c>
     </row>
     <row r="433">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>39.20994567871094</v>
+        <v>39.20993804931641</v>
       </c>
     </row>
     <row r="435">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>38.84883880615234</v>
+        <v>38.84884262084961</v>
       </c>
     </row>
     <row r="436">
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>38.55820465087891</v>
+        <v>38.55820083618164</v>
       </c>
     </row>
     <row r="437">
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>37.95931243896484</v>
+        <v>37.95930099487305</v>
       </c>
     </row>
     <row r="438">
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>37.78316879272461</v>
+        <v>37.78316116333008</v>
       </c>
     </row>
     <row r="439">
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>38.24114608764648</v>
+        <v>38.24113464355469</v>
       </c>
     </row>
     <row r="441">
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>38.83123016357422</v>
+        <v>38.83122253417969</v>
       </c>
     </row>
     <row r="443">
@@ -4875,7 +4875,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>39.33324432373047</v>
+        <v>39.33323669433594</v>
       </c>
     </row>
     <row r="447">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>40.71598434448242</v>
+        <v>40.71597671508789</v>
       </c>
     </row>
     <row r="451">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>40.27561187744141</v>
+        <v>40.27561950683594</v>
       </c>
     </row>
     <row r="453">
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>39.9849853515625</v>
+        <v>39.98497772216797</v>
       </c>
     </row>
     <row r="454">
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>40.12589645385742</v>
+        <v>40.12590408325195</v>
       </c>
     </row>
     <row r="455">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>40.01140975952148</v>
+        <v>40.01141357421875</v>
       </c>
     </row>
     <row r="456">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>40.45177459716797</v>
+        <v>40.45176315307617</v>
       </c>
     </row>
     <row r="457">
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>40.55745315551758</v>
+        <v>40.55744934082031</v>
       </c>
     </row>
     <row r="459">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>40.79524993896484</v>
+        <v>40.79524612426758</v>
       </c>
     </row>
     <row r="460">
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>40.44295501708984</v>
+        <v>40.44295120239258</v>
       </c>
     </row>
     <row r="462">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>39.43013000488281</v>
+        <v>39.43012237548828</v>
       </c>
     </row>
     <row r="463">
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>39.82645034790039</v>
+        <v>39.82645416259766</v>
       </c>
     </row>
     <row r="464">
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>39.37727737426758</v>
+        <v>39.37728118896484</v>
       </c>
     </row>
     <row r="465">
@@ -5075,7 +5075,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>40.05543518066406</v>
+        <v>40.05544281005859</v>
       </c>
     </row>
     <row r="467">
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>41.31488037109375</v>
+        <v>41.31487655639648</v>
       </c>
     </row>
     <row r="468">
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>42.21322250366211</v>
+        <v>42.21321868896484</v>
       </c>
     </row>
     <row r="470">
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>41.97542953491211</v>
+        <v>41.97542572021484</v>
       </c>
     </row>
     <row r="474">
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>43.09394073486328</v>
+        <v>43.09394454956055</v>
       </c>
     </row>
     <row r="476">
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>43.04991149902344</v>
+        <v>43.04990386962891</v>
       </c>
     </row>
     <row r="477">
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>42.90018081665039</v>
+        <v>42.90019226074219</v>
       </c>
     </row>
     <row r="478">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>43.32292938232422</v>
+        <v>43.32293319702148</v>
       </c>
     </row>
     <row r="481">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>44.07155227661133</v>
+        <v>44.07154846191406</v>
       </c>
     </row>
     <row r="484">
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>42.91780090332031</v>
+        <v>42.91780471801758</v>
       </c>
     </row>
     <row r="485">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>43.7632942199707</v>
+        <v>43.76330184936523</v>
       </c>
     </row>
     <row r="486">
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>44.32696914672852</v>
+        <v>44.32696533203125</v>
       </c>
     </row>
     <row r="488">
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>44.78493881225586</v>
+        <v>44.78494262695312</v>
       </c>
     </row>
     <row r="489">
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>44.78493881225586</v>
+        <v>44.78494262695312</v>
       </c>
     </row>
     <row r="490">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>44.98750686645508</v>
+        <v>44.98751068115234</v>
       </c>
     </row>
     <row r="493">
@@ -5345,7 +5345,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>44.67044830322266</v>
+        <v>44.67044448852539</v>
       </c>
     </row>
     <row r="494">
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>44.43819427490234</v>
+        <v>44.43819808959961</v>
       </c>
     </row>
     <row r="495">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>44.91870498657227</v>
+        <v>44.9187126159668</v>
       </c>
     </row>
     <row r="496">
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>45.13227081298828</v>
+        <v>45.13226699829102</v>
       </c>
     </row>
     <row r="497">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>45.37252044677734</v>
+        <v>45.37252807617188</v>
       </c>
     </row>
     <row r="499">
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>44.70515060424805</v>
+        <v>44.70514678955078</v>
       </c>
     </row>
     <row r="500">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>44.34920501708984</v>
+        <v>44.34921646118164</v>
       </c>
     </row>
     <row r="501">
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>44.80302429199219</v>
+        <v>44.80302810668945</v>
       </c>
     </row>
     <row r="502">
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>44.60726928710938</v>
+        <v>44.60726547241211</v>
       </c>
     </row>
     <row r="503">
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>44.73184585571289</v>
+        <v>44.73183822631836</v>
       </c>
     </row>
     <row r="504">
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>45.39921951293945</v>
+        <v>45.39920806884766</v>
       </c>
     </row>
     <row r="505">
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>46.00430297851562</v>
+        <v>46.00429916381836</v>
       </c>
     </row>
     <row r="506">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>45.97760391235352</v>
+        <v>45.97760772705078</v>
       </c>
     </row>
     <row r="507">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>46.27124786376953</v>
+        <v>46.27125549316406</v>
       </c>
     </row>
     <row r="508">
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>47.38353729248047</v>
+        <v>47.38354110717773</v>
       </c>
     </row>
     <row r="509">
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>48.68269348144531</v>
+        <v>48.68270111083984</v>
       </c>
     </row>
     <row r="512">
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>48.02421951293945</v>
+        <v>48.02422332763672</v>
       </c>
     </row>
     <row r="513">
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>48.49583053588867</v>
+        <v>48.49583435058594</v>
       </c>
     </row>
     <row r="514">
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>48.60260772705078</v>
+        <v>48.60261154174805</v>
       </c>
     </row>
     <row r="515">
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>49.05642700195312</v>
+        <v>49.05642318725586</v>
       </c>
     </row>
     <row r="516">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>48.36235427856445</v>
+        <v>48.36235046386719</v>
       </c>
     </row>
     <row r="517">
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>49.16321182250977</v>
+        <v>49.1632080078125</v>
       </c>
     </row>
     <row r="518">
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>50.11532974243164</v>
+        <v>50.11532211303711</v>
       </c>
     </row>
     <row r="520">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>49.67930603027344</v>
+        <v>49.6793098449707</v>
       </c>
     </row>
     <row r="521">
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>50.05303573608398</v>
+        <v>50.05303955078125</v>
       </c>
     </row>
     <row r="522">
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>49.68821334838867</v>
+        <v>49.68820571899414</v>
       </c>
     </row>
     <row r="523">
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>48.3089599609375</v>
+        <v>48.30896759033203</v>
       </c>
     </row>
     <row r="524">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>47.43693542480469</v>
+        <v>47.43693161010742</v>
       </c>
     </row>
     <row r="526">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>48.71829223632812</v>
+        <v>48.71828460693359</v>
       </c>
     </row>
     <row r="527">
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>49.35006332397461</v>
+        <v>49.35006713867188</v>
       </c>
     </row>
     <row r="528">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>49.59922027587891</v>
+        <v>49.59921646118164</v>
       </c>
     </row>
     <row r="529">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>49.61701583862305</v>
+        <v>49.61701965332031</v>
       </c>
     </row>
     <row r="530">
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>50.04413986206055</v>
+        <v>50.04413604736328</v>
       </c>
     </row>
     <row r="531">
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>50.13312149047852</v>
+        <v>50.13311767578125</v>
       </c>
     </row>
     <row r="532">
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>50.84498977661133</v>
+        <v>50.84498596191406</v>
       </c>
     </row>
     <row r="534">
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>51.43228149414062</v>
+        <v>51.43227767944336</v>
       </c>
     </row>
     <row r="536">
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>51.55684280395508</v>
+        <v>51.55685424804688</v>
       </c>
     </row>
     <row r="537">
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>51.57465362548828</v>
+        <v>51.57465744018555</v>
       </c>
     </row>
     <row r="538">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>50.86278533935547</v>
+        <v>50.8627815246582</v>
       </c>
     </row>
     <row r="539">
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>51.1920166015625</v>
+        <v>51.19202423095703</v>
       </c>
     </row>
     <row r="540">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>49.68821334838867</v>
+        <v>49.68820571899414</v>
       </c>
     </row>
     <row r="541">
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>49.91065979003906</v>
+        <v>49.91066360473633</v>
       </c>
     </row>
     <row r="542">
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>48.46023941040039</v>
+        <v>48.46023178100586</v>
       </c>
     </row>
     <row r="544">
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>47.8106575012207</v>
+        <v>47.81065368652344</v>
       </c>
     </row>
     <row r="545">
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>48.61151123046875</v>
+        <v>48.61150741577148</v>
       </c>
     </row>
     <row r="547">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>48.51362991333008</v>
+        <v>48.51362609863281</v>
       </c>
     </row>
     <row r="548">
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>47.38353729248047</v>
+        <v>47.38354110717773</v>
       </c>
     </row>
     <row r="549">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>47.8996467590332</v>
+        <v>47.89965057373047</v>
       </c>
     </row>
     <row r="550">
@@ -5915,7 +5915,7 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>46.60939407348633</v>
+        <v>46.6093864440918</v>
       </c>
     </row>
     <row r="551">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>47.41913604736328</v>
+        <v>47.41913223266602</v>
       </c>
     </row>
     <row r="553">
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>48.9140510559082</v>
+        <v>48.91405868530273</v>
       </c>
     </row>
     <row r="554">
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>48.04201126098633</v>
+        <v>48.04201889038086</v>
       </c>
     </row>
     <row r="555">
@@ -5975,7 +5975,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>48.36235427856445</v>
+        <v>48.36235046386719</v>
       </c>
     </row>
     <row r="557">
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>48.42464065551758</v>
+        <v>48.42464447021484</v>
       </c>
     </row>
     <row r="558">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>47.53480911254883</v>
+        <v>47.53480529785156</v>
       </c>
     </row>
     <row r="559">
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>47.9797248840332</v>
+        <v>47.97972869873047</v>
       </c>
     </row>
     <row r="561">
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>47.06320190429688</v>
+        <v>47.06319427490234</v>
       </c>
     </row>
     <row r="562">
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>45.98650360107422</v>
+        <v>45.98650741577148</v>
       </c>
     </row>
     <row r="563">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>47.40134048461914</v>
+        <v>47.40134429931641</v>
       </c>
     </row>
     <row r="565">
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>47.07209014892578</v>
+        <v>47.07209777832031</v>
       </c>
     </row>
     <row r="566">
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>47.22336959838867</v>
+        <v>47.2233772277832</v>
       </c>
     </row>
     <row r="567">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>47.92634201049805</v>
+        <v>47.92633819580078</v>
       </c>
     </row>
     <row r="569">
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>48.11320495605469</v>
+        <v>48.11320114135742</v>
       </c>
     </row>
     <row r="570">
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>48.38014984130859</v>
+        <v>48.38015365600586</v>
       </c>
     </row>
     <row r="571">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>47.66828536987305</v>
+        <v>47.66828918457031</v>
       </c>
     </row>
     <row r="572">
@@ -6135,7 +6135,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>48.059814453125</v>
+        <v>48.05981063842773</v>
       </c>
     </row>
     <row r="573">
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>47.65049362182617</v>
+        <v>47.65048980712891</v>
       </c>
     </row>
     <row r="574">
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>47.36574554443359</v>
+        <v>47.36573791503906</v>
       </c>
     </row>
     <row r="575">
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>47.56150436401367</v>
+        <v>47.56151580810547</v>
       </c>
     </row>
     <row r="576">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>48.36235427856445</v>
+        <v>48.36235046386719</v>
       </c>
     </row>
     <row r="579">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>48.18439102172852</v>
+        <v>48.18438720703125</v>
       </c>
     </row>
     <row r="580">
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>47.79286956787109</v>
+        <v>47.79286193847656</v>
       </c>
     </row>
     <row r="581">
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>48.08650970458984</v>
+        <v>48.08650588989258</v>
       </c>
     </row>
     <row r="582">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>47.91743850708008</v>
+        <v>47.91744232177734</v>
       </c>
     </row>
     <row r="583">
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>48.61151123046875</v>
+        <v>48.61150741577148</v>
       </c>
     </row>
     <row r="584">
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>48.67379379272461</v>
+        <v>48.67379760742188</v>
       </c>
     </row>
     <row r="585">
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>48.89625930786133</v>
+        <v>48.8962516784668</v>
       </c>
     </row>
     <row r="588">
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>48.03312301635742</v>
+        <v>48.03311538696289</v>
       </c>
     </row>
     <row r="589">
@@ -6305,7 +6305,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>48.03312301635742</v>
+        <v>48.03311538696289</v>
       </c>
     </row>
     <row r="590">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>47.7127799987793</v>
+        <v>47.71277618408203</v>
       </c>
     </row>
     <row r="592">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>48.16659164428711</v>
+        <v>48.16659545898438</v>
       </c>
     </row>
     <row r="593">
@@ -6345,7 +6345,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>48.66489410400391</v>
+        <v>48.66489028930664</v>
       </c>
     </row>
     <row r="594">
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>47.79286956787109</v>
+        <v>47.79286193847656</v>
       </c>
     </row>
     <row r="595">
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>47.65939331054688</v>
+        <v>47.65938568115234</v>
       </c>
     </row>
     <row r="596">
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>46.34243774414062</v>
+        <v>46.34244155883789</v>
       </c>
     </row>
     <row r="597">
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>47.07209014892578</v>
+        <v>47.07209777832031</v>
       </c>
     </row>
     <row r="600">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>47.70388031005859</v>
+        <v>47.70388412475586</v>
       </c>
     </row>
     <row r="601">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>47.56150436401367</v>
+        <v>47.56151580810547</v>
       </c>
     </row>
     <row r="602">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>47.83735275268555</v>
+        <v>47.83735656738281</v>
       </c>
     </row>
     <row r="603">
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>47.28566360473633</v>
+        <v>47.28565979003906</v>
       </c>
     </row>
     <row r="604">
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>47.67718505859375</v>
+        <v>47.67719268798828</v>
       </c>
     </row>
     <row r="605">
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>48.14879989624023</v>
+        <v>48.14879608154297</v>
       </c>
     </row>
     <row r="606">
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>48.51362991333008</v>
+        <v>48.51362609863281</v>
       </c>
     </row>
     <row r="608">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>48.82506561279297</v>
+        <v>48.82506942749023</v>
       </c>
     </row>
     <row r="609">
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>49.83057403564453</v>
+        <v>49.8305778503418</v>
       </c>
     </row>
     <row r="610">
@@ -6515,7 +6515,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>49.91065979003906</v>
+        <v>49.91066360473633</v>
       </c>
     </row>
     <row r="611">
@@ -6525,7 +6525,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>49.37676239013672</v>
+        <v>49.37677001953125</v>
       </c>
     </row>
     <row r="612">
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>49.82168197631836</v>
+        <v>49.82167816162109</v>
       </c>
     </row>
     <row r="613">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>49.57252883911133</v>
+        <v>49.5725212097168</v>
       </c>
     </row>
     <row r="614">
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>49.33227157592773</v>
+        <v>49.332275390625</v>
       </c>
     </row>
     <row r="615">
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>49.18990325927734</v>
+        <v>49.18989562988281</v>
       </c>
     </row>
     <row r="616">
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>49.58403396606445</v>
+        <v>49.58403015136719</v>
       </c>
     </row>
     <row r="617">
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>49.41422653198242</v>
+        <v>49.41423034667969</v>
       </c>
     </row>
     <row r="618">
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>49.54827880859375</v>
+        <v>49.54828262329102</v>
       </c>
     </row>
     <row r="619">
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>49.20867156982422</v>
+        <v>49.20866775512695</v>
       </c>
     </row>
     <row r="620">
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>48.53836822509766</v>
+        <v>48.53837585449219</v>
       </c>
     </row>
     <row r="621">
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>48.80649185180664</v>
+        <v>48.80648803710938</v>
       </c>
     </row>
     <row r="622">
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>48.46687316894531</v>
+        <v>48.46686935424805</v>
       </c>
     </row>
     <row r="623">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>48.67243576049805</v>
+        <v>48.67242431640625</v>
       </c>
     </row>
     <row r="624">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>48.44900131225586</v>
+        <v>48.44899368286133</v>
       </c>
     </row>
     <row r="625">
@@ -6675,7 +6675,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>49.19079208374023</v>
+        <v>49.1907958984375</v>
       </c>
     </row>
     <row r="627">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>49.60190963745117</v>
+        <v>49.60190200805664</v>
       </c>
     </row>
     <row r="628">
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>49.64659118652344</v>
+        <v>49.6465950012207</v>
       </c>
     </row>
     <row r="629">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>49.61084747314453</v>
+        <v>49.61083984375</v>
       </c>
     </row>
     <row r="630">
@@ -6715,7 +6715,7 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>49.28910446166992</v>
+        <v>49.28910064697266</v>
       </c>
     </row>
     <row r="631">
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>49.01203918457031</v>
+        <v>49.01204681396484</v>
       </c>
     </row>
     <row r="632">
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>48.95842742919922</v>
+        <v>48.95841979980469</v>
       </c>
     </row>
     <row r="633">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>48.10044860839844</v>
+        <v>48.10044097900391</v>
       </c>
     </row>
     <row r="634">
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>47.04584503173828</v>
+        <v>47.04584121704102</v>
       </c>
     </row>
     <row r="636">
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>47.85913848876953</v>
+        <v>47.85913467407227</v>
       </c>
     </row>
     <row r="637">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>47.94850921630859</v>
+        <v>47.94851303100586</v>
       </c>
     </row>
     <row r="639">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>47.8948860168457</v>
+        <v>47.89488220214844</v>
       </c>
     </row>
     <row r="642">
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>47.09052658081055</v>
+        <v>47.09053039550781</v>
       </c>
     </row>
     <row r="643">
@@ -6845,7 +6845,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>47.24246597290039</v>
+        <v>47.24246978759766</v>
       </c>
     </row>
     <row r="644">
@@ -6855,7 +6855,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>47.54632949829102</v>
+        <v>47.54633331298828</v>
       </c>
     </row>
     <row r="645">
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>47.63570404052734</v>
+        <v>47.63570785522461</v>
       </c>
     </row>
     <row r="646">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>46.03593826293945</v>
+        <v>46.03593063354492</v>
       </c>
     </row>
     <row r="648">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>45.10646438598633</v>
+        <v>45.1064567565918</v>
       </c>
     </row>
     <row r="649">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>46.33086776733398</v>
+        <v>46.33086013793945</v>
       </c>
     </row>
     <row r="650">
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>46.44704818725586</v>
+        <v>46.44705200195312</v>
       </c>
     </row>
     <row r="653">
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>46.6436653137207</v>
+        <v>46.64366912841797</v>
       </c>
     </row>
     <row r="654">
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>46.88497161865234</v>
+        <v>46.88497543334961</v>
       </c>
     </row>
     <row r="655">
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>46.81348037719727</v>
+        <v>46.81347274780273</v>
       </c>
     </row>
     <row r="656">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>46.42023086547852</v>
+        <v>46.42023468017578</v>
       </c>
     </row>
     <row r="657">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>46.57217025756836</v>
+        <v>46.57217407226562</v>
       </c>
     </row>
     <row r="658">
@@ -6995,7 +6995,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>46.63473129272461</v>
+        <v>46.63472747802734</v>
       </c>
     </row>
     <row r="659">
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>46.3487434387207</v>
+        <v>46.34873962402344</v>
       </c>
     </row>
     <row r="661">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>46.23255157470703</v>
+        <v>46.23254776000977</v>
       </c>
     </row>
     <row r="662">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>45.8125</v>
+        <v>45.81249237060547</v>
       </c>
     </row>
     <row r="663">
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>45.04389572143555</v>
+        <v>45.04389190673828</v>
       </c>
     </row>
     <row r="665">
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>44.23953628540039</v>
+        <v>44.23954010009766</v>
       </c>
     </row>
     <row r="667">
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>44.90983581542969</v>
+        <v>44.90983200073242</v>
       </c>
     </row>
     <row r="668">
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>45.9823112487793</v>
+        <v>45.98230743408203</v>
       </c>
     </row>
     <row r="670">
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>46.84029006958008</v>
+        <v>46.84028625488281</v>
       </c>
     </row>
     <row r="674">
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>47.43909072875977</v>
+        <v>47.43908309936523</v>
       </c>
     </row>
     <row r="675">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>47.22459030151367</v>
+        <v>47.22459411621094</v>
       </c>
     </row>
     <row r="676">
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>47.47483444213867</v>
+        <v>47.47483825683594</v>
       </c>
     </row>
     <row r="677">
@@ -7185,7 +7185,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>47.75189208984375</v>
+        <v>47.75188827514648</v>
       </c>
     </row>
     <row r="678">
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>46.6436653137207</v>
+        <v>46.64366912841797</v>
       </c>
     </row>
     <row r="683">
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>46.63473129272461</v>
+        <v>46.63472747802734</v>
       </c>
     </row>
     <row r="684">
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>44.67747116088867</v>
+        <v>44.67746734619141</v>
       </c>
     </row>
     <row r="687">
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>45.00814819335938</v>
+        <v>45.00815200805664</v>
       </c>
     </row>
     <row r="688">
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>45.57118988037109</v>
+        <v>45.57119369506836</v>
       </c>
     </row>
     <row r="689">
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>45.08857727050781</v>
+        <v>45.08858108520508</v>
       </c>
     </row>
     <row r="693">
@@ -7355,7 +7355,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>45.02602386474609</v>
+        <v>45.02602005004883</v>
       </c>
     </row>
     <row r="695">
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>44.98133850097656</v>
+        <v>44.9813346862793</v>
       </c>
     </row>
     <row r="696">
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>44.31997299194336</v>
+        <v>44.31996917724609</v>
       </c>
     </row>
     <row r="697">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>45.24944686889648</v>
+        <v>45.24945068359375</v>
       </c>
     </row>
     <row r="700">
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>45.41926193237305</v>
+        <v>45.41926574707031</v>
       </c>
     </row>
     <row r="701">
@@ -7425,7 +7425,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>45.32988739013672</v>
+        <v>45.32988357543945</v>
       </c>
     </row>
     <row r="702">
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>45.7231330871582</v>
+        <v>45.72312545776367</v>
       </c>
     </row>
     <row r="704">
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>45.86612319946289</v>
+        <v>45.86612701416016</v>
       </c>
     </row>
     <row r="705">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>46.42023086547852</v>
+        <v>46.42023468017578</v>
       </c>
     </row>
     <row r="706">
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>46.30404663085938</v>
+        <v>46.30405044555664</v>
       </c>
     </row>
     <row r="707">
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>46.92072296142578</v>
+        <v>46.92072677612305</v>
       </c>
     </row>
     <row r="708">
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>46.60791778564453</v>
+        <v>46.6079216003418</v>
       </c>
     </row>
     <row r="710">
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>46.50960922241211</v>
+        <v>46.50960540771484</v>
       </c>
     </row>
     <row r="711">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>46.75091171264648</v>
+        <v>46.75091934204102</v>
       </c>
     </row>
     <row r="712">
@@ -7535,7 +7535,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>46.50960922241211</v>
+        <v>46.50960540771484</v>
       </c>
     </row>
     <row r="713">
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>46.17892837524414</v>
+        <v>46.17892456054688</v>
       </c>
     </row>
     <row r="715">
@@ -7565,7 +7565,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>45.50863265991211</v>
+        <v>45.50862503051758</v>
       </c>
     </row>
     <row r="716">
@@ -7575,7 +7575,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>45.86612319946289</v>
+        <v>45.86612701416016</v>
       </c>
     </row>
     <row r="717">
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>45.45501327514648</v>
+        <v>45.45500946044922</v>
       </c>
     </row>
     <row r="718">
@@ -7605,7 +7605,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>45.56225967407227</v>
+        <v>45.562255859375</v>
       </c>
     </row>
     <row r="720">
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>45.50863265991211</v>
+        <v>45.50862503051758</v>
       </c>
     </row>
     <row r="721">
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>45.74993515014648</v>
+        <v>45.74994277954102</v>
       </c>
     </row>
     <row r="723">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>45.56225967407227</v>
+        <v>45.562255859375</v>
       </c>
     </row>
     <row r="724">
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>46.3487434387207</v>
+        <v>46.34873962402344</v>
       </c>
     </row>
     <row r="725">
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>46.47385787963867</v>
+        <v>46.47386169433594</v>
       </c>
     </row>
     <row r="726">
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>46.38448333740234</v>
+        <v>46.38448715209961</v>
       </c>
     </row>
     <row r="728">
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>46.1431770324707</v>
+        <v>46.14318084716797</v>
       </c>
     </row>
     <row r="729">
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>45.58013153076172</v>
+        <v>45.58012771606445</v>
       </c>
     </row>
     <row r="730">
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>45.50863265991211</v>
+        <v>45.50862503051758</v>
       </c>
     </row>
     <row r="731">
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>45.1422004699707</v>
+        <v>45.14220809936523</v>
       </c>
     </row>
     <row r="732">
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>43.69436645507812</v>
+        <v>43.69436264038086</v>
       </c>
     </row>
     <row r="736">
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>43.64967346191406</v>
+        <v>43.64968109130859</v>
       </c>
     </row>
     <row r="737">
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>44.34678649902344</v>
+        <v>44.34678268432617</v>
       </c>
     </row>
     <row r="739">
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>43.7211799621582</v>
+        <v>43.72116851806641</v>
       </c>
     </row>
     <row r="740">
@@ -7815,7 +7815,7 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>44.06079483032227</v>
+        <v>44.060791015625</v>
       </c>
     </row>
     <row r="741">
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>44.72215270996094</v>
+        <v>44.72214889526367</v>
       </c>
     </row>
     <row r="744">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>43.94837188720703</v>
+        <v>43.94837951660156</v>
       </c>
     </row>
     <row r="747">
@@ -7905,7 +7905,7 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>43.65828704833984</v>
+        <v>43.65827941894531</v>
       </c>
     </row>
     <row r="750">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>43.93931198120117</v>
+        <v>43.93930435180664</v>
       </c>
     </row>
     <row r="753">
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>44.16593551635742</v>
+        <v>44.16594314575195</v>
       </c>
     </row>
     <row r="754">
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="B754" t="n">
-        <v>44.36537551879883</v>
+        <v>44.36537170410156</v>
       </c>
     </row>
     <row r="755">
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>44.62496948242188</v>
+        <v>44.62496566772461</v>
       </c>
     </row>
     <row r="760">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>44.47077178955078</v>
+        <v>44.47077560424805</v>
       </c>
     </row>
     <row r="761">
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>43.74516296386719</v>
+        <v>43.74515914916992</v>
       </c>
     </row>
     <row r="762">
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>44.34379196166992</v>
+        <v>44.34378814697266</v>
       </c>
     </row>
     <row r="764">
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>44.34379196166992</v>
+        <v>44.34378814697266</v>
       </c>
     </row>
     <row r="765">
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="B765" t="n">
-        <v>45.36872100830078</v>
+        <v>45.36871337890625</v>
       </c>
     </row>
     <row r="766">
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>46.12152862548828</v>
+        <v>46.12153625488281</v>
       </c>
     </row>
     <row r="767">
@@ -8085,7 +8085,7 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>45.46848678588867</v>
+        <v>45.46849060058594</v>
       </c>
     </row>
     <row r="768">
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>44.44356155395508</v>
+        <v>44.44356536865234</v>
       </c>
     </row>
     <row r="773">
@@ -8155,7 +8155,7 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>43.73609924316406</v>
+        <v>43.7360954284668</v>
       </c>
     </row>
     <row r="775">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="B777" t="n">
-        <v>42.89257431030273</v>
+        <v>42.892578125</v>
       </c>
     </row>
     <row r="778">
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>44.5705451965332</v>
+        <v>44.57053756713867</v>
       </c>
     </row>
     <row r="780">
@@ -8215,7 +8215,7 @@
         </is>
       </c>
       <c r="B780" t="n">
-        <v>44.49798965454102</v>
+        <v>44.49798583984375</v>
       </c>
     </row>
     <row r="781">
@@ -8225,7 +8225,7 @@
         </is>
       </c>
       <c r="B781" t="n">
-        <v>44.02633666992188</v>
+        <v>44.02634048461914</v>
       </c>
     </row>
     <row r="782">
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="B783" t="n">
-        <v>44.04448318481445</v>
+        <v>44.04447937011719</v>
       </c>
     </row>
     <row r="784">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="B784" t="n">
-        <v>44.47077178955078</v>
+        <v>44.47077560424805</v>
       </c>
     </row>
     <row r="785">
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>45.16917419433594</v>
+        <v>45.16917037963867</v>
       </c>
     </row>
     <row r="786">
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="B787" t="n">
-        <v>44.18959808349609</v>
+        <v>44.18960189819336</v>
       </c>
     </row>
     <row r="788">
@@ -8325,7 +8325,7 @@
         </is>
       </c>
       <c r="B791" t="n">
-        <v>44.6340446472168</v>
+        <v>44.63403701782227</v>
       </c>
     </row>
     <row r="792">
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="B792" t="n">
-        <v>44.18959808349609</v>
+        <v>44.18960189819336</v>
       </c>
     </row>
     <row r="793">
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="B793" t="n">
-        <v>43.56376266479492</v>
+        <v>43.56375885009766</v>
       </c>
     </row>
     <row r="794">
@@ -8355,7 +8355,7 @@
         </is>
       </c>
       <c r="B794" t="n">
-        <v>43.05583572387695</v>
+        <v>43.05583953857422</v>
       </c>
     </row>
     <row r="795">
@@ -8375,7 +8375,7 @@
         </is>
       </c>
       <c r="B796" t="n">
-        <v>42.94699859619141</v>
+        <v>42.94699478149414</v>
       </c>
     </row>
     <row r="797">
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="B797" t="n">
-        <v>42.3846435546875</v>
+        <v>42.38464736938477</v>
       </c>
     </row>
     <row r="798">
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="B798" t="n">
-        <v>41.82230377197266</v>
+        <v>41.82229614257812</v>
       </c>
     </row>
     <row r="799">
@@ -8405,7 +8405,7 @@
         </is>
       </c>
       <c r="B799" t="n">
-        <v>41.89486312866211</v>
+        <v>41.89485931396484</v>
       </c>
     </row>
     <row r="800">
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="B800" t="n">
-        <v>41.30530548095703</v>
+        <v>41.30530166625977</v>
       </c>
     </row>
     <row r="801">
@@ -8425,7 +8425,7 @@
         </is>
       </c>
       <c r="B801" t="n">
-        <v>40.47085571289062</v>
+        <v>40.47085952758789</v>
       </c>
     </row>
     <row r="802">
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="B803" t="n">
-        <v>39.08312225341797</v>
+        <v>39.08312606811523</v>
       </c>
     </row>
     <row r="804">
@@ -8455,7 +8455,7 @@
         </is>
       </c>
       <c r="B804" t="n">
-        <v>40.18968963623047</v>
+        <v>40.18968200683594</v>
       </c>
     </row>
     <row r="805">
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="B805" t="n">
-        <v>39.43685150146484</v>
+        <v>39.43685913085938</v>
       </c>
     </row>
     <row r="806">
@@ -8495,7 +8495,7 @@
         </is>
       </c>
       <c r="B808" t="n">
-        <v>37.73167419433594</v>
+        <v>37.7316780090332</v>
       </c>
     </row>
     <row r="809">
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="B810" t="n">
-        <v>40.56155776977539</v>
+        <v>40.56155395507812</v>
       </c>
     </row>
     <row r="811">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="B813" t="n">
-        <v>41.2418098449707</v>
+        <v>41.24181747436523</v>
       </c>
     </row>
     <row r="814">
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B815" t="n">
-        <v>41.18740081787109</v>
+        <v>41.18739318847656</v>
       </c>
     </row>
     <row r="816">
@@ -8585,7 +8585,7 @@
         </is>
       </c>
       <c r="B817" t="n">
-        <v>40.99691772460938</v>
+        <v>40.99692153930664</v>
       </c>
     </row>
     <row r="818">
@@ -8595,7 +8595,7 @@
         </is>
       </c>
       <c r="B818" t="n">
-        <v>41.6953239440918</v>
+        <v>41.69532012939453</v>
       </c>
     </row>
     <row r="819">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="B821" t="n">
-        <v>41.63182830810547</v>
+        <v>41.6318359375</v>
       </c>
     </row>
     <row r="822">
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="B824" t="n">
-        <v>41.04226684570312</v>
+        <v>41.04226303100586</v>
       </c>
     </row>
     <row r="825">
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="B825" t="n">
-        <v>40.71574401855469</v>
+        <v>40.71574783325195</v>
       </c>
     </row>
     <row r="826">
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="B827" t="n">
-        <v>40.24409484863281</v>
+        <v>40.24410247802734</v>
       </c>
     </row>
     <row r="828">
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="B829" t="n">
-        <v>40.64319229125977</v>
+        <v>40.64318466186523</v>
       </c>
     </row>
     <row r="830">
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="B831" t="n">
-        <v>39.98106384277344</v>
+        <v>39.9810676574707</v>
       </c>
     </row>
     <row r="832">
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="B832" t="n">
-        <v>39.78153228759766</v>
+        <v>39.78152465820312</v>
       </c>
     </row>
     <row r="833">
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="B834" t="n">
-        <v>38.78381729125977</v>
+        <v>38.7838134765625</v>
       </c>
     </row>
     <row r="835">
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="B835" t="n">
-        <v>38.43914413452148</v>
+        <v>38.43915176391602</v>
       </c>
     </row>
     <row r="836">
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="B838" t="n">
-        <v>37.75889205932617</v>
+        <v>37.75889587402344</v>
       </c>
     </row>
     <row r="839">
@@ -8805,7 +8805,7 @@
         </is>
       </c>
       <c r="B839" t="n">
-        <v>38.30309677124023</v>
+        <v>38.30309295654297</v>
       </c>
     </row>
     <row r="840">
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="B840" t="n">
-        <v>38.43914413452148</v>
+        <v>38.43915176391602</v>
       </c>
     </row>
     <row r="841">
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="B843" t="n">
-        <v>39.08312225341797</v>
+        <v>39.08312606811523</v>
       </c>
     </row>
     <row r="844">
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="B844" t="n">
-        <v>37.64097595214844</v>
+        <v>37.64097213745117</v>
       </c>
     </row>
     <row r="845">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="B845" t="n">
-        <v>37.12398529052734</v>
+        <v>37.12397766113281</v>
       </c>
     </row>
     <row r="846">
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="B846" t="n">
-        <v>36.05370712280273</v>
+        <v>36.0537109375</v>
       </c>
     </row>
     <row r="847">
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="B847" t="n">
-        <v>36.22603988647461</v>
+        <v>36.22603607177734</v>
       </c>
     </row>
     <row r="848">
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B848" t="n">
-        <v>35.97208023071289</v>
+        <v>35.97207641601562</v>
       </c>
     </row>
     <row r="849">
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="B849" t="n">
-        <v>35.73625564575195</v>
+        <v>35.73625183105469</v>
       </c>
     </row>
     <row r="850">
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="B850" t="n">
-        <v>36.72489547729492</v>
+        <v>36.72489929199219</v>
       </c>
     </row>
     <row r="851">
@@ -8925,7 +8925,7 @@
         </is>
       </c>
       <c r="B851" t="n">
-        <v>36.57977676391602</v>
+        <v>36.57977294921875</v>
       </c>
     </row>
     <row r="852">
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="B852" t="n">
-        <v>37.47771835327148</v>
+        <v>37.47771072387695</v>
       </c>
     </row>
     <row r="853">
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="B853" t="n">
-        <v>36.57977676391602</v>
+        <v>36.57977294921875</v>
       </c>
     </row>
     <row r="854">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="B855" t="n">
-        <v>37.31444931030273</v>
+        <v>37.314453125</v>
       </c>
     </row>
     <row r="856">
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="B858" t="n">
-        <v>37.12398529052734</v>
+        <v>37.12397766113281</v>
       </c>
     </row>
     <row r="859">
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="B860" t="n">
-        <v>38.13983535766602</v>
+        <v>38.13984298706055</v>
       </c>
     </row>
     <row r="861">
@@ -9055,7 +9055,7 @@
         </is>
       </c>
       <c r="B864" t="n">
-        <v>38.43008041381836</v>
+        <v>38.43007659912109</v>
       </c>
     </row>
     <row r="865">
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="B865" t="n">
-        <v>38.6386833190918</v>
+        <v>38.63868713378906</v>
       </c>
     </row>
     <row r="866">
@@ -9075,7 +9075,7 @@
         </is>
       </c>
       <c r="B866" t="n">
-        <v>38.75660705566406</v>
+        <v>38.7566032409668</v>
       </c>
     </row>
     <row r="867">
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B867" t="n">
-        <v>38.96521377563477</v>
+        <v>38.9652099609375</v>
       </c>
     </row>
     <row r="868">
@@ -9095,7 +9095,7 @@
         </is>
       </c>
       <c r="B868" t="n">
-        <v>38.04317855834961</v>
+        <v>38.04318237304688</v>
       </c>
     </row>
     <row r="869">
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="B870" t="n">
-        <v>36.30521011352539</v>
+        <v>36.30520629882812</v>
       </c>
     </row>
     <row r="871">
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="B871" t="n">
-        <v>36.80830764770508</v>
+        <v>36.80831146240234</v>
       </c>
     </row>
     <row r="872">
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="B872" t="n">
-        <v>37.29310607910156</v>
+        <v>37.2931022644043</v>
       </c>
     </row>
     <row r="873">
@@ -9145,7 +9145,7 @@
         </is>
       </c>
       <c r="B873" t="n">
-        <v>36.14971160888672</v>
+        <v>36.14970779418945</v>
       </c>
     </row>
     <row r="874">
@@ -9165,7 +9165,7 @@
         </is>
       </c>
       <c r="B875" t="n">
-        <v>36.87233352661133</v>
+        <v>36.87233734130859</v>
       </c>
     </row>
     <row r="876">
@@ -9175,7 +9175,7 @@
         </is>
       </c>
       <c r="B876" t="n">
-        <v>36.2137336730957</v>
+        <v>36.21373748779297</v>
       </c>
     </row>
     <row r="877">
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="B877" t="n">
-        <v>36.32350158691406</v>
+        <v>36.32350540161133</v>
       </c>
     </row>
     <row r="878">
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="B880" t="n">
-        <v>37.00039291381836</v>
+        <v>37.00039672851562</v>
       </c>
     </row>
     <row r="881">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="B882" t="n">
-        <v>36.68024826049805</v>
+        <v>36.68024444580078</v>
       </c>
     </row>
     <row r="883">
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c r="B883" t="n">
-        <v>36.45156097412109</v>
+        <v>36.45156478881836</v>
       </c>
     </row>
     <row r="884">
@@ -9255,7 +9255,7 @@
         </is>
       </c>
       <c r="B884" t="n">
-        <v>36.16799926757812</v>
+        <v>36.16800308227539</v>
       </c>
     </row>
     <row r="885">
@@ -9265,7 +9265,7 @@
         </is>
       </c>
       <c r="B885" t="n">
-        <v>35.94846343994141</v>
+        <v>35.94846725463867</v>
       </c>
     </row>
     <row r="886">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="B888" t="n">
-        <v>35.69234466552734</v>
+        <v>35.69235229492188</v>
       </c>
     </row>
     <row r="889">
@@ -9305,7 +9305,7 @@
         </is>
       </c>
       <c r="B889" t="n">
-        <v>35.55513763427734</v>
+        <v>35.55514144897461</v>
       </c>
     </row>
     <row r="890">
@@ -9315,7 +9315,7 @@
         </is>
       </c>
       <c r="B890" t="n">
-        <v>35.47281265258789</v>
+        <v>35.47281646728516</v>
       </c>
     </row>
     <row r="891">
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="B891" t="n">
-        <v>35.15267181396484</v>
+        <v>35.15266036987305</v>
       </c>
     </row>
     <row r="892">
@@ -9335,7 +9335,7 @@
         </is>
       </c>
       <c r="B892" t="n">
-        <v>35.33560562133789</v>
+        <v>35.33560943603516</v>
       </c>
     </row>
     <row r="893">
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="B893" t="n">
-        <v>35.58257675170898</v>
+        <v>35.58258438110352</v>
       </c>
     </row>
     <row r="894">
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="B894" t="n">
-        <v>36.16799926757812</v>
+        <v>36.16800308227539</v>
       </c>
     </row>
     <row r="895">
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="B895" t="n">
-        <v>36.01250076293945</v>
+        <v>36.01249694824219</v>
       </c>
     </row>
     <row r="896">
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="B896" t="n">
-        <v>36.42412185668945</v>
+        <v>36.42412567138672</v>
       </c>
     </row>
     <row r="897">
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="B897" t="n">
-        <v>36.0582275390625</v>
+        <v>36.05823516845703</v>
       </c>
     </row>
     <row r="898">
@@ -9395,7 +9395,7 @@
         </is>
       </c>
       <c r="B898" t="n">
-        <v>36.18629455566406</v>
+        <v>36.18629837036133</v>
       </c>
     </row>
     <row r="899">
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="B899" t="n">
-        <v>35.90273284912109</v>
+        <v>35.90273666381836</v>
       </c>
     </row>
     <row r="900">
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="B901" t="n">
-        <v>36.72597885131836</v>
+        <v>36.72598648071289</v>
       </c>
     </row>
     <row r="902">
@@ -9445,7 +9445,7 @@
         </is>
       </c>
       <c r="B903" t="n">
-        <v>36.24117660522461</v>
+        <v>36.24118041992188</v>
       </c>
     </row>
     <row r="904">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="B906" t="n">
-        <v>36.6070671081543</v>
+        <v>36.60707092285156</v>
       </c>
     </row>
     <row r="907">
@@ -9485,7 +9485,7 @@
         </is>
       </c>
       <c r="B907" t="n">
-        <v>36.64366149902344</v>
+        <v>36.64365005493164</v>
       </c>
     </row>
     <row r="908">
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="B908" t="n">
-        <v>36.68939590454102</v>
+        <v>36.68939208984375</v>
       </c>
     </row>
     <row r="909">
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="B911" t="n">
-        <v>37.15590286254883</v>
+        <v>37.15589904785156</v>
       </c>
     </row>
     <row r="912">
@@ -9555,7 +9555,7 @@
         </is>
       </c>
       <c r="B914" t="n">
-        <v>37.36628341674805</v>
+        <v>37.36627960205078</v>
       </c>
     </row>
     <row r="915">
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="B916" t="n">
-        <v>37.00039291381836</v>
+        <v>37.00039672851562</v>
       </c>
     </row>
     <row r="917">
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="B918" t="n">
-        <v>36.17715072631836</v>
+        <v>36.17714691162109</v>
       </c>
     </row>
     <row r="919">
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="B919" t="n">
-        <v>36.36923599243164</v>
+        <v>36.36924362182617</v>
       </c>
     </row>
     <row r="920">
@@ -9615,7 +9615,7 @@
         </is>
       </c>
       <c r="B920" t="n">
-        <v>36.36009216308594</v>
+        <v>36.3600959777832</v>
       </c>
     </row>
     <row r="921">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="B921" t="n">
-        <v>37.14675521850586</v>
+        <v>37.14675903320312</v>
       </c>
     </row>
     <row r="922">
@@ -9645,7 +9645,7 @@
         </is>
       </c>
       <c r="B923" t="n">
-        <v>36.36923599243164</v>
+        <v>36.36924362182617</v>
       </c>
     </row>
     <row r="924">
@@ -9655,7 +9655,7 @@
         </is>
       </c>
       <c r="B924" t="n">
-        <v>35.93932342529297</v>
+        <v>35.93932723999023</v>
       </c>
     </row>
     <row r="925">
@@ -9675,7 +9675,7 @@
         </is>
       </c>
       <c r="B926" t="n">
-        <v>35.7838249206543</v>
+        <v>35.78381729125977</v>
       </c>
     </row>
     <row r="927">
@@ -9685,7 +9685,7 @@
         </is>
       </c>
       <c r="B927" t="n">
-        <v>35.45452117919922</v>
+        <v>35.45451736450195</v>
       </c>
     </row>
     <row r="928">
@@ -9695,7 +9695,7 @@
         </is>
       </c>
       <c r="B928" t="n">
-        <v>35.03374481201172</v>
+        <v>35.03374862670898</v>
       </c>
     </row>
     <row r="929">
@@ -9715,7 +9715,7 @@
         </is>
       </c>
       <c r="B930" t="n">
-        <v>35.15267181396484</v>
+        <v>35.15266036987305</v>
       </c>
     </row>
     <row r="931">
@@ -9745,7 +9745,7 @@
         </is>
       </c>
       <c r="B933" t="n">
-        <v>35.08863830566406</v>
+        <v>35.0886344909668</v>
       </c>
     </row>
     <row r="934">
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="B934" t="n">
-        <v>35.26243209838867</v>
+        <v>35.26242446899414</v>
       </c>
     </row>
     <row r="935">
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="B936" t="n">
-        <v>34.56724166870117</v>
+        <v>34.56724548339844</v>
       </c>
     </row>
     <row r="937">
@@ -9805,7 +9805,7 @@
         </is>
       </c>
       <c r="B939" t="n">
-        <v>33.90864562988281</v>
+        <v>33.90864944458008</v>
       </c>
     </row>
     <row r="940">
@@ -9835,7 +9835,7 @@
         </is>
       </c>
       <c r="B942" t="n">
-        <v>32.50912094116211</v>
+        <v>32.50912475585938</v>
       </c>
     </row>
     <row r="943">
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="B946" t="n">
-        <v>31.9054126739502</v>
+        <v>31.90540885925293</v>
       </c>
     </row>
     <row r="947">
@@ -9885,7 +9885,7 @@
         </is>
       </c>
       <c r="B947" t="n">
-        <v>32.42680358886719</v>
+        <v>32.42679977416992</v>
       </c>
     </row>
     <row r="948">
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="B948" t="n">
-        <v>33.48788070678711</v>
+        <v>33.48787689208984</v>
       </c>
     </row>
     <row r="949">
@@ -9905,7 +9905,7 @@
         </is>
       </c>
       <c r="B949" t="n">
-        <v>33.50616073608398</v>
+        <v>33.50616836547852</v>
       </c>
     </row>
     <row r="950">
@@ -9915,7 +9915,7 @@
         </is>
       </c>
       <c r="B950" t="n">
-        <v>33.304931640625</v>
+        <v>33.30492782592773</v>
       </c>
     </row>
     <row r="951">
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="B951" t="n">
-        <v>32.60974502563477</v>
+        <v>32.6097412109375</v>
       </c>
     </row>
     <row r="952">
@@ -9935,7 +9935,7 @@
         </is>
       </c>
       <c r="B952" t="n">
-        <v>32.15238189697266</v>
+        <v>32.15238571166992</v>
       </c>
     </row>
     <row r="953">
@@ -9945,7 +9945,7 @@
         </is>
       </c>
       <c r="B953" t="n">
-        <v>31.6401424407959</v>
+        <v>31.64014434814453</v>
       </c>
     </row>
     <row r="954">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="B954" t="n">
-        <v>31.67673492431641</v>
+        <v>31.67672920227051</v>
       </c>
     </row>
     <row r="955">
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="B955" t="n">
-        <v>31.76820182800293</v>
+        <v>31.76819801330566</v>
       </c>
     </row>
     <row r="956">
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="B956" t="n">
-        <v>31.29254722595215</v>
+        <v>31.29254531860352</v>
       </c>
     </row>
     <row r="957">
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="B957" t="n">
-        <v>32.15238189697266</v>
+        <v>32.15238571166992</v>
       </c>
     </row>
     <row r="958">
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="B958" t="n">
-        <v>32.16153717041016</v>
+        <v>32.16153335571289</v>
       </c>
     </row>
     <row r="959">
@@ -10015,7 +10015,7 @@
         </is>
       </c>
       <c r="B960" t="n">
-        <v>31.77735328674316</v>
+        <v>31.77735137939453</v>
       </c>
     </row>
     <row r="961">
@@ -10025,7 +10025,7 @@
         </is>
       </c>
       <c r="B961" t="n">
-        <v>32.26214981079102</v>
+        <v>32.26214599609375</v>
       </c>
     </row>
     <row r="962">
@@ -10035,7 +10035,7 @@
         </is>
       </c>
       <c r="B962" t="n">
-        <v>31.03642463684082</v>
+        <v>31.03642845153809</v>
       </c>
     </row>
     <row r="963">
@@ -10045,7 +10045,7 @@
         </is>
       </c>
       <c r="B963" t="n">
-        <v>31.29254722595215</v>
+        <v>31.29254531860352</v>
       </c>
     </row>
     <row r="964">
@@ -10055,7 +10055,7 @@
         </is>
       </c>
       <c r="B964" t="n">
-        <v>31.80479431152344</v>
+        <v>31.80479049682617</v>
       </c>
     </row>
     <row r="965">
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="B965" t="n">
-        <v>31.55781364440918</v>
+        <v>31.55781745910645</v>
       </c>
     </row>
     <row r="966">
@@ -10075,7 +10075,7 @@
         </is>
       </c>
       <c r="B966" t="n">
-        <v>31.36572647094727</v>
+        <v>31.3657283782959</v>
       </c>
     </row>
     <row r="967">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="B967" t="n">
-        <v>31.27425003051758</v>
+        <v>31.27425193786621</v>
       </c>
     </row>
     <row r="968">
@@ -10095,7 +10095,7 @@
         </is>
       </c>
       <c r="B968" t="n">
-        <v>31.85052680969238</v>
+        <v>31.85053062438965</v>
       </c>
     </row>
     <row r="969">
@@ -10105,7 +10105,7 @@
         </is>
       </c>
       <c r="B969" t="n">
-        <v>31.58525276184082</v>
+        <v>31.58526039123535</v>
       </c>
     </row>
     <row r="970">
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="B970" t="n">
-        <v>31.76820182800293</v>
+        <v>31.76819801330566</v>
       </c>
     </row>
     <row r="971">
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B971" t="n">
-        <v>33.11283493041992</v>
+        <v>33.11284255981445</v>
       </c>
     </row>
     <row r="972">
@@ -10135,7 +10135,7 @@
         </is>
       </c>
       <c r="B972" t="n">
-        <v>33.13113403320312</v>
+        <v>33.13113784790039</v>
       </c>
     </row>
     <row r="973">
@@ -10145,7 +10145,7 @@
         </is>
       </c>
       <c r="B973" t="n">
-        <v>33.36896133422852</v>
+        <v>33.36895751953125</v>
       </c>
     </row>
     <row r="974">
@@ -10155,7 +10155,7 @@
         </is>
       </c>
       <c r="B974" t="n">
-        <v>32.79268646240234</v>
+        <v>32.79268264770508</v>
       </c>
     </row>
     <row r="975">
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="B975" t="n">
-        <v>33.98181915283203</v>
+        <v>33.9818229675293</v>
       </c>
     </row>
     <row r="976">
@@ -10175,7 +10175,7 @@
         </is>
       </c>
       <c r="B976" t="n">
-        <v>34.90568923950195</v>
+        <v>34.90568542480469</v>
       </c>
     </row>
     <row r="977">
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="B977" t="n">
-        <v>34.6953010559082</v>
+        <v>34.69530487060547</v>
       </c>
     </row>
     <row r="978">
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="B978" t="n">
-        <v>35.49110794067383</v>
+        <v>35.49110412597656</v>
       </c>
     </row>
     <row r="979">
@@ -10205,7 +10205,7 @@
         </is>
       </c>
       <c r="B979" t="n">
-        <v>34.92398071289062</v>
+        <v>34.92398452758789</v>
       </c>
     </row>
     <row r="980">
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="B981" t="n">
-        <v>34.78677749633789</v>
+        <v>34.78676986694336</v>
       </c>
     </row>
     <row r="982">
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="B982" t="n">
-        <v>34.34770965576172</v>
+        <v>34.34770584106445</v>
       </c>
     </row>
     <row r="983">
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="B983" t="n">
-        <v>34.43003463745117</v>
+        <v>34.43003845214844</v>
       </c>
     </row>
     <row r="984">
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="B984" t="n">
-        <v>34.71360015869141</v>
+        <v>34.71359634399414</v>
       </c>
     </row>
     <row r="985">
@@ -10265,7 +10265,7 @@
         </is>
       </c>
       <c r="B985" t="n">
-        <v>34.5489501953125</v>
+        <v>34.54895401000977</v>
       </c>
     </row>
     <row r="986">
@@ -10275,7 +10275,7 @@
         </is>
       </c>
       <c r="B986" t="n">
-        <v>34.39344024658203</v>
+        <v>34.39344787597656</v>
       </c>
     </row>
     <row r="987">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="B987" t="n">
-        <v>35.13436889648438</v>
+        <v>35.13436508178711</v>
       </c>
     </row>
     <row r="988">
@@ -10295,7 +10295,7 @@
         </is>
       </c>
       <c r="B988" t="n">
-        <v>36.14971160888672</v>
+        <v>36.14970779418945</v>
       </c>
     </row>
     <row r="989">
@@ -10315,7 +10315,7 @@
         </is>
       </c>
       <c r="B990" t="n">
-        <v>36.16799926757812</v>
+        <v>36.16800308227539</v>
       </c>
     </row>
     <row r="991">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="B992" t="n">
-        <v>35.71064376831055</v>
+        <v>35.71064758300781</v>
       </c>
     </row>
     <row r="993">
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="B993" t="n">
-        <v>35.50026321411133</v>
+        <v>35.5002555847168</v>
       </c>
     </row>
     <row r="994">
@@ -10355,7 +10355,7 @@
         </is>
       </c>
       <c r="B994" t="n">
-        <v>35.93016815185547</v>
+        <v>35.93017196655273</v>
       </c>
     </row>
     <row r="995">
@@ -10365,7 +10365,7 @@
         </is>
       </c>
       <c r="B995" t="n">
-        <v>35.69234466552734</v>
+        <v>35.69235229492188</v>
       </c>
     </row>
     <row r="996">
@@ -10375,7 +10375,7 @@
         </is>
       </c>
       <c r="B996" t="n">
-        <v>35.58257675170898</v>
+        <v>35.58258438110352</v>
       </c>
     </row>
     <row r="997">
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="B1000" t="n">
-        <v>35.13125610351562</v>
+        <v>35.13125228881836</v>
       </c>
     </row>
     <row r="1001">
@@ -10425,7 +10425,7 @@
         </is>
       </c>
       <c r="B1001" t="n">
-        <v>35.15911102294922</v>
+        <v>35.15911483764648</v>
       </c>
     </row>
     <row r="1002">
@@ -10465,7 +10465,7 @@
         </is>
       </c>
       <c r="B1005" t="n">
-        <v>35.1033935546875</v>
+        <v>35.10338973999023</v>
       </c>
     </row>
     <row r="1006">
@@ -10475,7 +10475,7 @@
         </is>
       </c>
       <c r="B1006" t="n">
-        <v>35.62344741821289</v>
+        <v>35.62344360351562</v>
       </c>
     </row>
     <row r="1007">
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="B1007" t="n">
-        <v>35.1033935546875</v>
+        <v>35.10338973999023</v>
       </c>
     </row>
     <row r="1008">
@@ -10495,7 +10495,7 @@
         </is>
       </c>
       <c r="B1008" t="n">
-        <v>35.68845367431641</v>
+        <v>35.68844604492188</v>
       </c>
     </row>
     <row r="1009">
@@ -10505,7 +10505,7 @@
         </is>
       </c>
       <c r="B1009" t="n">
-        <v>35.19626235961914</v>
+        <v>35.19625854492188</v>
       </c>
     </row>
     <row r="1010">
@@ -10525,7 +10525,7 @@
         </is>
       </c>
       <c r="B1011" t="n">
-        <v>36.56139373779297</v>
+        <v>36.5613899230957</v>
       </c>
     </row>
     <row r="1012">
@@ -10535,7 +10535,7 @@
         </is>
       </c>
       <c r="B1012" t="n">
-        <v>36.449951171875</v>
+        <v>36.44995498657227</v>
       </c>
     </row>
     <row r="1013">
@@ -10545,7 +10545,7 @@
         </is>
       </c>
       <c r="B1013" t="n">
-        <v>37.21145248413086</v>
+        <v>37.21144866943359</v>
       </c>
     </row>
     <row r="1014">
@@ -10565,7 +10565,7 @@
         </is>
       </c>
       <c r="B1015" t="n">
-        <v>37.75936889648438</v>
+        <v>37.75936508178711</v>
       </c>
     </row>
     <row r="1016">
@@ -10585,7 +10585,7 @@
         </is>
       </c>
       <c r="B1017" t="n">
-        <v>38.10296630859375</v>
+        <v>38.10297012329102</v>
       </c>
     </row>
     <row r="1018">
@@ -10625,7 +10625,7 @@
         </is>
       </c>
       <c r="B1021" t="n">
-        <v>38.16797637939453</v>
+        <v>38.16796875</v>
       </c>
     </row>
     <row r="1022">
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="B1023" t="n">
-        <v>39.03163146972656</v>
+        <v>39.0316276550293</v>
       </c>
     </row>
     <row r="1024">
@@ -10655,7 +10655,7 @@
         </is>
       </c>
       <c r="B1024" t="n">
-        <v>39.05949401855469</v>
+        <v>39.05949020385742</v>
       </c>
     </row>
     <row r="1025">
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="B1025" t="n">
-        <v>39.09663009643555</v>
+        <v>39.09663391113281</v>
       </c>
     </row>
     <row r="1026">
@@ -10675,7 +10675,7 @@
         </is>
       </c>
       <c r="B1026" t="n">
-        <v>39.46809768676758</v>
+        <v>39.46810150146484</v>
       </c>
     </row>
     <row r="1027">
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="B1027" t="n">
-        <v>39.28236770629883</v>
+        <v>39.28236389160156</v>
       </c>
     </row>
     <row r="1028">
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="B1031" t="n">
-        <v>38.65087509155273</v>
+        <v>38.65087890625</v>
       </c>
     </row>
     <row r="1032">
@@ -10735,7 +10735,7 @@
         </is>
       </c>
       <c r="B1032" t="n">
-        <v>37.96366882324219</v>
+        <v>37.96367263793945</v>
       </c>
     </row>
     <row r="1033">
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="B1033" t="n">
-        <v>37.40647125244141</v>
+        <v>37.40647506713867</v>
       </c>
     </row>
     <row r="1034">
@@ -10755,7 +10755,7 @@
         </is>
       </c>
       <c r="B1034" t="n">
-        <v>37.55506134033203</v>
+        <v>37.5550537109375</v>
       </c>
     </row>
     <row r="1035">
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="B1036" t="n">
-        <v>37.68507385253906</v>
+        <v>37.6850700378418</v>
       </c>
     </row>
     <row r="1037">
@@ -10785,7 +10785,7 @@
         </is>
       </c>
       <c r="B1037" t="n">
-        <v>37.32289505004883</v>
+        <v>37.32289123535156</v>
       </c>
     </row>
     <row r="1038">
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="B1038" t="n">
-        <v>37.62935256958008</v>
+        <v>37.62935638427734</v>
       </c>
     </row>
     <row r="1039">
@@ -10805,7 +10805,7 @@
         </is>
       </c>
       <c r="B1039" t="n">
-        <v>37.56435012817383</v>
+        <v>37.5643424987793</v>
       </c>
     </row>
     <row r="1040">
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="B1043" t="n">
-        <v>36.38494873046875</v>
+        <v>36.38494110107422</v>
       </c>
     </row>
     <row r="1044">
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="B1045" t="n">
-        <v>36.38494873046875</v>
+        <v>36.38494110107422</v>
       </c>
     </row>
     <row r="1046">
@@ -10885,7 +10885,7 @@
         </is>
       </c>
       <c r="B1047" t="n">
-        <v>35.75345611572266</v>
+        <v>35.75345993041992</v>
       </c>
     </row>
     <row r="1048">
@@ -10895,7 +10895,7 @@
         </is>
       </c>
       <c r="B1048" t="n">
-        <v>35.50271224975586</v>
+        <v>35.50272369384766</v>
       </c>
     </row>
     <row r="1049">
@@ -10905,7 +10905,7 @@
         </is>
       </c>
       <c r="B1049" t="n">
-        <v>36.26422119140625</v>
+        <v>36.26421737670898</v>
       </c>
     </row>
     <row r="1050">
@@ -10925,7 +10925,7 @@
         </is>
       </c>
       <c r="B1051" t="n">
-        <v>36.71926879882812</v>
+        <v>36.71926498413086</v>
       </c>
     </row>
     <row r="1052">
@@ -10935,7 +10935,7 @@
         </is>
       </c>
       <c r="B1052" t="n">
-        <v>36.58924865722656</v>
+        <v>36.58925247192383</v>
       </c>
     </row>
     <row r="1053">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="B1053" t="n">
-        <v>35.97633361816406</v>
+        <v>35.97633743286133</v>
       </c>
     </row>
     <row r="1054">
@@ -10955,7 +10955,7 @@
         </is>
       </c>
       <c r="B1054" t="n">
-        <v>36.12492370605469</v>
+        <v>36.12491989135742</v>
       </c>
     </row>
     <row r="1055">
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="B1056" t="n">
-        <v>35.14053726196289</v>
+        <v>35.14054107666016</v>
       </c>
     </row>
     <row r="1057">
@@ -10985,7 +10985,7 @@
         </is>
       </c>
       <c r="B1057" t="n">
-        <v>35.19626235961914</v>
+        <v>35.19625854492188</v>
       </c>
     </row>
     <row r="1058">
@@ -10995,7 +10995,7 @@
         </is>
       </c>
       <c r="B1058" t="n">
-        <v>35.21483612060547</v>
+        <v>35.21482849121094</v>
       </c>
     </row>
     <row r="1059">
@@ -11015,7 +11015,7 @@
         </is>
       </c>
       <c r="B1060" t="n">
-        <v>35.14053726196289</v>
+        <v>35.14054107666016</v>
       </c>
     </row>
     <row r="1061">
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="B1063" t="n">
-        <v>35.37270736694336</v>
+        <v>35.37270355224609</v>
       </c>
     </row>
     <row r="1064">
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="B1065" t="n">
-        <v>36.00419235229492</v>
+        <v>36.00419616699219</v>
       </c>
     </row>
     <row r="1066">
@@ -11075,7 +11075,7 @@
         </is>
       </c>
       <c r="B1066" t="n">
-        <v>35.91133117675781</v>
+        <v>35.91132354736328</v>
       </c>
     </row>
     <row r="1067">
@@ -11115,7 +11115,7 @@
         </is>
       </c>
       <c r="B1070" t="n">
-        <v>36.69140243530273</v>
+        <v>36.69139862060547</v>
       </c>
     </row>
     <row r="1071">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B1072" t="n">
-        <v>36.71926879882812</v>
+        <v>36.71926498413086</v>
       </c>
     </row>
     <row r="1073">
@@ -11145,7 +11145,7 @@
         </is>
       </c>
       <c r="B1073" t="n">
-        <v>36.71926879882812</v>
+        <v>36.71926498413086</v>
       </c>
     </row>
     <row r="1074">
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="B1074" t="n">
-        <v>36.43137359619141</v>
+        <v>36.43138122558594</v>
       </c>
     </row>
     <row r="1075">
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="B1075" t="n">
-        <v>36.5799674987793</v>
+        <v>36.57995986938477</v>
       </c>
     </row>
     <row r="1076">
@@ -11175,7 +11175,7 @@
         </is>
       </c>
       <c r="B1076" t="n">
-        <v>36.61710739135742</v>
+        <v>36.61711120605469</v>
       </c>
     </row>
     <row r="1077">
@@ -11185,7 +11185,7 @@
         </is>
       </c>
       <c r="B1077" t="n">
-        <v>36.83998489379883</v>
+        <v>36.83998870849609</v>
       </c>
     </row>
     <row r="1078">
@@ -11195,7 +11195,7 @@
         </is>
       </c>
       <c r="B1078" t="n">
-        <v>36.5799674987793</v>
+        <v>36.57995986938477</v>
       </c>
     </row>
     <row r="1079">
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="B1080" t="n">
-        <v>36.88642120361328</v>
+        <v>36.88642501831055</v>
       </c>
     </row>
     <row r="1081">
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="B1081" t="n">
-        <v>37.04429626464844</v>
+        <v>37.04429244995117</v>
       </c>
     </row>
     <row r="1082">
@@ -11235,7 +11235,7 @@
         </is>
       </c>
       <c r="B1082" t="n">
-        <v>36.99785995483398</v>
+        <v>36.99786376953125</v>
       </c>
     </row>
     <row r="1083">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="B1086" t="n">
-        <v>36.14348983764648</v>
+        <v>36.14349365234375</v>
       </c>
     </row>
     <row r="1087">
@@ -11295,7 +11295,7 @@
         </is>
       </c>
       <c r="B1088" t="n">
-        <v>35.66988372802734</v>
+        <v>35.66987228393555</v>
       </c>
     </row>
     <row r="1089">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="B1089" t="n">
-        <v>36.15278244018555</v>
+        <v>36.15277862548828</v>
       </c>
     </row>
     <row r="1090">
@@ -11315,7 +11315,7 @@
         </is>
       </c>
       <c r="B1090" t="n">
-        <v>36.33851623535156</v>
+        <v>36.3385124206543</v>
       </c>
     </row>
     <row r="1091">
@@ -11325,7 +11325,7 @@
         </is>
       </c>
       <c r="B1091" t="n">
-        <v>36.21778106689453</v>
+        <v>36.2177848815918</v>
       </c>
     </row>
     <row r="1092">
@@ -11345,7 +11345,7 @@
         </is>
       </c>
       <c r="B1093" t="n">
-        <v>35.80917358398438</v>
+        <v>35.80918121337891</v>
       </c>
     </row>
     <row r="1094">
@@ -11355,7 +11355,7 @@
         </is>
       </c>
       <c r="B1094" t="n">
-        <v>36.0970573425293</v>
+        <v>36.09706115722656</v>
       </c>
     </row>
     <row r="1095">
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="B1095" t="n">
-        <v>36.5799674987793</v>
+        <v>36.57995986938477</v>
       </c>
     </row>
     <row r="1096">
@@ -11375,7 +11375,7 @@
         </is>
       </c>
       <c r="B1096" t="n">
-        <v>36.59853744506836</v>
+        <v>36.59853363037109</v>
       </c>
     </row>
     <row r="1097">
@@ -11385,7 +11385,7 @@
         </is>
       </c>
       <c r="B1097" t="n">
-        <v>36.37565612792969</v>
+        <v>36.37565994262695</v>
       </c>
     </row>
     <row r="1098">
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="B1098" t="n">
-        <v>36.35708999633789</v>
+        <v>36.35708236694336</v>
       </c>
     </row>
     <row r="1099">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="B1102" t="n">
-        <v>36.19921112060547</v>
+        <v>36.19921875</v>
       </c>
     </row>
     <row r="1103">
@@ -11445,7 +11445,7 @@
         </is>
       </c>
       <c r="B1103" t="n">
-        <v>36.36637115478516</v>
+        <v>36.36637496948242</v>
       </c>
     </row>
     <row r="1104">
@@ -11465,7 +11465,7 @@
         </is>
       </c>
       <c r="B1105" t="n">
-        <v>36.19921112060547</v>
+        <v>36.19921875</v>
       </c>
     </row>
     <row r="1106">
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="B1106" t="n">
-        <v>36.49638748168945</v>
+        <v>36.49638366699219</v>
       </c>
     </row>
     <row r="1107">
@@ -11495,7 +11495,7 @@
         </is>
       </c>
       <c r="B1108" t="n">
-        <v>35.66059112548828</v>
+        <v>35.66058731079102</v>
       </c>
     </row>
     <row r="1109">
@@ -11505,7 +11505,7 @@
         </is>
       </c>
       <c r="B1109" t="n">
-        <v>35.5862922668457</v>
+        <v>35.58629989624023</v>
       </c>
     </row>
     <row r="1110">
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="B1110" t="n">
-        <v>36.21778106689453</v>
+        <v>36.2177848815918</v>
       </c>
     </row>
     <row r="1111">
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="B1113" t="n">
-        <v>36.0970573425293</v>
+        <v>36.09706115722656</v>
       </c>
     </row>
     <row r="1114">
@@ -11555,7 +11555,7 @@
         </is>
       </c>
       <c r="B1114" t="n">
-        <v>36.71926879882812</v>
+        <v>36.71926498413086</v>
       </c>
     </row>
     <row r="1115">
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="B1115" t="n">
-        <v>36.7099723815918</v>
+        <v>36.70997619628906</v>
       </c>
     </row>
     <row r="1116">
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="B1116" t="n">
-        <v>37.03500747680664</v>
+        <v>37.03501129150391</v>
       </c>
     </row>
     <row r="1117">
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="B1117" t="n">
-        <v>36.87590408325195</v>
+        <v>36.87590026855469</v>
       </c>
     </row>
     <row r="1118">
@@ -11615,7 +11615,7 @@
         </is>
       </c>
       <c r="B1120" t="n">
-        <v>37.38130569458008</v>
+        <v>37.38130187988281</v>
       </c>
     </row>
     <row r="1121">
@@ -11625,7 +11625,7 @@
         </is>
       </c>
       <c r="B1121" t="n">
-        <v>37.75568008422852</v>
+        <v>37.75568389892578</v>
       </c>
     </row>
     <row r="1122">
@@ -11655,7 +11655,7 @@
         </is>
       </c>
       <c r="B1124" t="n">
-        <v>38.26108169555664</v>
+        <v>38.26108932495117</v>
       </c>
     </row>
     <row r="1125">
@@ -11705,7 +11705,7 @@
         </is>
       </c>
       <c r="B1129" t="n">
-        <v>36.78230285644531</v>
+        <v>36.78230667114258</v>
       </c>
     </row>
     <row r="1130">
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="B1133" t="n">
-        <v>37.02565002441406</v>
+        <v>37.02565383911133</v>
       </c>
     </row>
     <row r="1134">
@@ -11755,7 +11755,7 @@
         </is>
       </c>
       <c r="B1134" t="n">
-        <v>37.43746566772461</v>
+        <v>37.43745803833008</v>
       </c>
     </row>
     <row r="1135">
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="B1135" t="n">
-        <v>37.21283340454102</v>
+        <v>37.21283721923828</v>
       </c>
     </row>
     <row r="1136">
@@ -11775,7 +11775,7 @@
         </is>
       </c>
       <c r="B1136" t="n">
-        <v>36.45473098754883</v>
+        <v>36.45472717285156</v>
       </c>
     </row>
     <row r="1137">
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="B1142" t="n">
-        <v>38.38275146484375</v>
+        <v>38.38275527954102</v>
       </c>
     </row>
     <row r="1143">
@@ -11865,7 +11865,7 @@
         </is>
       </c>
       <c r="B1145" t="n">
-        <v>38.07389450073242</v>
+        <v>38.07389831542969</v>
       </c>
     </row>
     <row r="1146">
@@ -11885,7 +11885,7 @@
         </is>
       </c>
       <c r="B1147" t="n">
-        <v>37.73696517944336</v>
+        <v>37.73696136474609</v>
       </c>
     </row>
     <row r="1148">
@@ -11905,7 +11905,7 @@
         </is>
       </c>
       <c r="B1149" t="n">
-        <v>38.56994247436523</v>
+        <v>38.5699462890625</v>
       </c>
     </row>
     <row r="1150">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="B1150" t="n">
-        <v>38.79457092285156</v>
+        <v>38.7945671081543</v>
       </c>
     </row>
     <row r="1151">
@@ -11925,7 +11925,7 @@
         </is>
       </c>
       <c r="B1151" t="n">
-        <v>38.31724548339844</v>
+        <v>38.31724166870117</v>
       </c>
     </row>
     <row r="1152">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="B1152" t="n">
-        <v>39.24381637573242</v>
+        <v>39.24382019042969</v>
       </c>
     </row>
     <row r="1153">
@@ -11955,7 +11955,7 @@
         </is>
       </c>
       <c r="B1154" t="n">
-        <v>38.76648712158203</v>
+        <v>38.76649475097656</v>
       </c>
     </row>
     <row r="1155">
@@ -11965,7 +11965,7 @@
         </is>
       </c>
       <c r="B1155" t="n">
-        <v>37.83991241455078</v>
+        <v>37.83991622924805</v>
       </c>
     </row>
     <row r="1156">
@@ -11985,7 +11985,7 @@
         </is>
       </c>
       <c r="B1157" t="n">
-        <v>37.94287109375</v>
+        <v>37.94286346435547</v>
       </c>
     </row>
     <row r="1158">
@@ -11995,7 +11995,7 @@
         </is>
       </c>
       <c r="B1158" t="n">
-        <v>37.8867073059082</v>
+        <v>37.88671112060547</v>
       </c>
     </row>
     <row r="1159">
@@ -12005,7 +12005,7 @@
         </is>
       </c>
       <c r="B1159" t="n">
-        <v>37.4281005859375</v>
+        <v>37.42810440063477</v>
       </c>
     </row>
     <row r="1160">
@@ -12025,7 +12025,7 @@
         </is>
       </c>
       <c r="B1161" t="n">
-        <v>37.57785034179688</v>
+        <v>37.57785797119141</v>
       </c>
     </row>
     <row r="1162">
@@ -12035,7 +12035,7 @@
         </is>
       </c>
       <c r="B1162" t="n">
-        <v>37.02565002441406</v>
+        <v>37.02565383911133</v>
       </c>
     </row>
     <row r="1163">
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="B1163" t="n">
-        <v>36.84782028198242</v>
+        <v>36.84781646728516</v>
       </c>
     </row>
     <row r="1164">
@@ -12085,7 +12085,7 @@
         </is>
       </c>
       <c r="B1167" t="n">
-        <v>35.93996810913086</v>
+        <v>35.93996429443359</v>
       </c>
     </row>
     <row r="1168">
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="B1168" t="n">
-        <v>36.02420043945312</v>
+        <v>36.02419662475586</v>
       </c>
     </row>
     <row r="1169">
@@ -12105,7 +12105,7 @@
         </is>
       </c>
       <c r="B1169" t="n">
-        <v>35.94932174682617</v>
+        <v>35.94931793212891</v>
       </c>
     </row>
     <row r="1170">
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="B1170" t="n">
-        <v>36.52024841308594</v>
+        <v>36.52024459838867</v>
       </c>
     </row>
     <row r="1171">
@@ -12145,7 +12145,7 @@
         </is>
       </c>
       <c r="B1173" t="n">
-        <v>36.77295303344727</v>
+        <v>36.77294921875</v>
       </c>
     </row>
     <row r="1174">
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="B1174" t="n">
-        <v>37.24091339111328</v>
+        <v>37.24091720581055</v>
       </c>
     </row>
     <row r="1175">
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="B1177" t="n">
-        <v>37.09116363525391</v>
+        <v>37.09116744995117</v>
       </c>
     </row>
     <row r="1178">
@@ -12195,7 +12195,7 @@
         </is>
       </c>
       <c r="B1178" t="n">
-        <v>36.79166412353516</v>
+        <v>36.79166793823242</v>
       </c>
     </row>
     <row r="1179">
@@ -12215,7 +12215,7 @@
         </is>
       </c>
       <c r="B1180" t="n">
-        <v>36.15522766113281</v>
+        <v>36.15523147583008</v>
       </c>
     </row>
     <row r="1181">
@@ -12225,7 +12225,7 @@
         </is>
       </c>
       <c r="B1181" t="n">
-        <v>36.23009872436523</v>
+        <v>36.2301025390625</v>
       </c>
     </row>
     <row r="1182">
@@ -12255,7 +12255,7 @@
         </is>
       </c>
       <c r="B1184" t="n">
-        <v>36.52024841308594</v>
+        <v>36.52024459838867</v>
       </c>
     </row>
     <row r="1185">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="B1185" t="n">
-        <v>36.76358413696289</v>
+        <v>36.76358032226562</v>
       </c>
     </row>
     <row r="1186">
@@ -12315,7 +12315,7 @@
         </is>
       </c>
       <c r="B1190" t="n">
-        <v>35.58430862426758</v>
+        <v>35.58430480957031</v>
       </c>
     </row>
     <row r="1191">
@@ -12335,7 +12335,7 @@
         </is>
       </c>
       <c r="B1192" t="n">
-        <v>35.84637451171875</v>
+        <v>35.84637069702148</v>
       </c>
     </row>
     <row r="1193">
@@ -12345,7 +12345,7 @@
         </is>
       </c>
       <c r="B1193" t="n">
-        <v>35.34096145629883</v>
+        <v>35.34095764160156</v>
       </c>
     </row>
     <row r="1194">
@@ -12355,7 +12355,7 @@
         </is>
       </c>
       <c r="B1194" t="n">
-        <v>35.39712142944336</v>
+        <v>35.39711761474609</v>
       </c>
     </row>
     <row r="1195">
@@ -12365,7 +12365,7 @@
         </is>
       </c>
       <c r="B1195" t="n">
-        <v>35.4907112121582</v>
+        <v>35.49071502685547</v>
       </c>
     </row>
     <row r="1196">
@@ -12375,7 +12375,7 @@
         </is>
       </c>
       <c r="B1196" t="n">
-        <v>35.51879501342773</v>
+        <v>35.5187873840332</v>
       </c>
     </row>
     <row r="1197">
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="B1197" t="n">
-        <v>35.34096145629883</v>
+        <v>35.34095764160156</v>
       </c>
     </row>
     <row r="1198">
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="B1200" t="n">
-        <v>34.90107345581055</v>
+        <v>34.90107727050781</v>
       </c>
     </row>
     <row r="1201">
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="B1203" t="n">
-        <v>35.74341583251953</v>
+        <v>35.7434196472168</v>
       </c>
     </row>
     <row r="1204">
@@ -12475,7 +12475,7 @@
         </is>
       </c>
       <c r="B1206" t="n">
-        <v>35.4345588684082</v>
+        <v>35.43455505371094</v>
       </c>
     </row>
     <row r="1207">
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="B1208" t="n">
-        <v>35.60302352905273</v>
+        <v>35.60302734375</v>
       </c>
     </row>
     <row r="1209">
@@ -12505,7 +12505,7 @@
         </is>
       </c>
       <c r="B1209" t="n">
-        <v>35.0601806640625</v>
+        <v>35.06018447875977</v>
       </c>
     </row>
     <row r="1210">
@@ -12515,7 +12515,7 @@
         </is>
       </c>
       <c r="B1210" t="n">
-        <v>34.85427856445312</v>
+        <v>34.85427474975586</v>
       </c>
     </row>
     <row r="1211">
@@ -12535,7 +12535,7 @@
         </is>
       </c>
       <c r="B1212" t="n">
-        <v>34.40502548217773</v>
+        <v>34.40502166748047</v>
       </c>
     </row>
     <row r="1213">
@@ -12545,7 +12545,7 @@
         </is>
       </c>
       <c r="B1213" t="n">
-        <v>34.84491729736328</v>
+        <v>34.84491348266602</v>
       </c>
     </row>
     <row r="1214">
@@ -12575,7 +12575,7 @@
         </is>
       </c>
       <c r="B1216" t="n">
-        <v>34.18975830078125</v>
+        <v>34.18976211547852</v>
       </c>
     </row>
     <row r="1217">
@@ -12625,7 +12625,7 @@
         </is>
       </c>
       <c r="B1221" t="n">
-        <v>35.99611663818359</v>
+        <v>35.99612045288086</v>
       </c>
     </row>
     <row r="1222">
@@ -12635,7 +12635,7 @@
         </is>
       </c>
       <c r="B1222" t="n">
-        <v>36.28625869750977</v>
+        <v>36.28626251220703</v>
       </c>
     </row>
     <row r="1223">
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="B1224" t="n">
-        <v>35.97739791870117</v>
+        <v>35.97740173339844</v>
       </c>
     </row>
     <row r="1225">
@@ -12675,7 +12675,7 @@
         </is>
       </c>
       <c r="B1226" t="n">
-        <v>35.89316940307617</v>
+        <v>35.89316558837891</v>
       </c>
     </row>
     <row r="1227">
@@ -12695,7 +12695,7 @@
         </is>
       </c>
       <c r="B1228" t="n">
-        <v>36.83845901489258</v>
+        <v>36.83846664428711</v>
       </c>
     </row>
     <row r="1229">
@@ -12705,7 +12705,7 @@
         </is>
       </c>
       <c r="B1229" t="n">
-        <v>37.14731597900391</v>
+        <v>37.14732360839844</v>
       </c>
     </row>
     <row r="1230">
@@ -12715,7 +12715,7 @@
         </is>
       </c>
       <c r="B1230" t="n">
-        <v>36.79166412353516</v>
+        <v>36.79166793823242</v>
       </c>
     </row>
     <row r="1231">
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="B1231" t="n">
-        <v>36.83845901489258</v>
+        <v>36.83846664428711</v>
       </c>
     </row>
     <row r="1232">
@@ -12735,7 +12735,7 @@
         </is>
       </c>
       <c r="B1232" t="n">
-        <v>37.29706954956055</v>
+        <v>37.29706573486328</v>
       </c>
     </row>
     <row r="1233">
@@ -12745,7 +12745,7 @@
         </is>
       </c>
       <c r="B1233" t="n">
-        <v>37.06308746337891</v>
+        <v>37.06308364868164</v>
       </c>
     </row>
     <row r="1234">
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="B1238" t="n">
-        <v>36.95077514648438</v>
+        <v>36.95077133178711</v>
       </c>
     </row>
     <row r="1239">
@@ -12805,7 +12805,7 @@
         </is>
       </c>
       <c r="B1239" t="n">
-        <v>37.02565002441406</v>
+        <v>37.02565383911133</v>
       </c>
     </row>
     <row r="1240">
@@ -12815,7 +12815,7 @@
         </is>
       </c>
       <c r="B1240" t="n">
-        <v>37.18476104736328</v>
+        <v>37.18475723266602</v>
       </c>
     </row>
     <row r="1241">
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="B1241" t="n">
-        <v>36.76358413696289</v>
+        <v>36.76358032226562</v>
       </c>
     </row>
     <row r="1242">
@@ -12835,7 +12835,7 @@
         </is>
       </c>
       <c r="B1242" t="n">
-        <v>36.53896331787109</v>
+        <v>36.53896713256836</v>
       </c>
     </row>
     <row r="1243">
@@ -12845,7 +12845,7 @@
         </is>
       </c>
       <c r="B1243" t="n">
-        <v>36.49216461181641</v>
+        <v>36.49216842651367</v>
       </c>
     </row>
     <row r="1244">
@@ -12855,7 +12855,7 @@
         </is>
       </c>
       <c r="B1244" t="n">
-        <v>36.66999053955078</v>
+        <v>36.66999435424805</v>
       </c>
     </row>
     <row r="1245">
@@ -12875,7 +12875,7 @@
         </is>
       </c>
       <c r="B1246" t="n">
-        <v>36.72615432739258</v>
+        <v>36.72615051269531</v>
       </c>
     </row>
     <row r="1247">
@@ -12905,7 +12905,7 @@
         </is>
       </c>
       <c r="B1249" t="n">
-        <v>37.64336776733398</v>
+        <v>37.64337158203125</v>
       </c>
     </row>
     <row r="1250">
@@ -12915,7 +12915,7 @@
         </is>
       </c>
       <c r="B1250" t="n">
-        <v>37.41873931884766</v>
+        <v>37.41874313354492</v>
       </c>
     </row>
     <row r="1251">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="B1251" t="n">
-        <v>37.40002059936523</v>
+        <v>37.40002822875977</v>
       </c>
     </row>
     <row r="1252">
@@ -12945,7 +12945,7 @@
         </is>
       </c>
       <c r="B1253" t="n">
-        <v>37.03925323486328</v>
+        <v>37.03924942016602</v>
       </c>
     </row>
     <row r="1254">
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="B1254" t="n">
-        <v>37.73540496826172</v>
+        <v>37.73540878295898</v>
       </c>
     </row>
     <row r="1255">
@@ -12965,7 +12965,7 @@
         </is>
       </c>
       <c r="B1255" t="n">
-        <v>37.55421829223633</v>
+        <v>37.55421447753906</v>
       </c>
     </row>
     <row r="1256">
@@ -12975,7 +12975,7 @@
         </is>
       </c>
       <c r="B1256" t="n">
-        <v>37.84983825683594</v>
+        <v>37.8498420715332</v>
       </c>
     </row>
     <row r="1257">
@@ -12995,7 +12995,7 @@
         </is>
       </c>
       <c r="B1258" t="n">
-        <v>38.36480331420898</v>
+        <v>38.36480712890625</v>
       </c>
     </row>
     <row r="1259">
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="B1261" t="n">
-        <v>37.68772506713867</v>
+        <v>37.68772888183594</v>
       </c>
     </row>
     <row r="1262">
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="B1263" t="n">
-        <v>37.61143112182617</v>
+        <v>37.61143493652344</v>
       </c>
     </row>
     <row r="1264">
@@ -13055,7 +13055,7 @@
         </is>
       </c>
       <c r="B1264" t="n">
-        <v>37.71633529663086</v>
+        <v>37.71633148193359</v>
       </c>
     </row>
     <row r="1265">
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="B1266" t="n">
-        <v>37.09646987915039</v>
+        <v>37.09647369384766</v>
       </c>
     </row>
     <row r="1267">
@@ -13145,7 +13145,7 @@
         </is>
       </c>
       <c r="B1273" t="n">
-        <v>36.2858772277832</v>
+        <v>36.28588104248047</v>
       </c>
     </row>
     <row r="1274">
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="B1274" t="n">
-        <v>36.60057830810547</v>
+        <v>36.60058212280273</v>
       </c>
     </row>
     <row r="1275">
@@ -13165,7 +13165,7 @@
         </is>
       </c>
       <c r="B1275" t="n">
-        <v>37.01064300537109</v>
+        <v>37.01064682006836</v>
       </c>
     </row>
     <row r="1276">
@@ -13185,7 +13185,7 @@
         </is>
       </c>
       <c r="B1277" t="n">
-        <v>37.08693695068359</v>
+        <v>37.08692932128906</v>
       </c>
     </row>
     <row r="1278">
@@ -13305,7 +13305,7 @@
         </is>
       </c>
       <c r="B1289" t="n">
-        <v>37.32534408569336</v>
+        <v>37.32534027099609</v>
       </c>
     </row>
     <row r="1290">
@@ -13335,7 +13335,7 @@
         </is>
       </c>
       <c r="B1292" t="n">
-        <v>38.22176361083984</v>
+        <v>38.22175979614258</v>
       </c>
     </row>
     <row r="1293">
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="B1297" t="n">
-        <v>38.54599380493164</v>
+        <v>38.54599761962891</v>
       </c>
     </row>
     <row r="1298">
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="B1298" t="n">
-        <v>38.62228775024414</v>
+        <v>38.62229156494141</v>
       </c>
     </row>
     <row r="1299">
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="B1302" t="n">
-        <v>38.51738739013672</v>
+        <v>38.51738357543945</v>
       </c>
     </row>
     <row r="1303">
@@ -13445,7 +13445,7 @@
         </is>
       </c>
       <c r="B1303" t="n">
-        <v>38.17407608032227</v>
+        <v>38.17407989501953</v>
       </c>
     </row>
     <row r="1304">
@@ -13455,7 +13455,7 @@
         </is>
       </c>
       <c r="B1304" t="n">
-        <v>38.72719192504883</v>
+        <v>38.72718811035156</v>
       </c>
     </row>
     <row r="1305">
@@ -13465,7 +13465,7 @@
         </is>
       </c>
       <c r="B1305" t="n">
-        <v>38.96560287475586</v>
+        <v>38.96559906005859</v>
       </c>
     </row>
     <row r="1306">
@@ -13475,7 +13475,7 @@
         </is>
       </c>
       <c r="B1306" t="n">
-        <v>38.92744827270508</v>
+        <v>38.92745208740234</v>
       </c>
     </row>
     <row r="1307">
@@ -13495,7 +13495,7 @@
         </is>
       </c>
       <c r="B1308" t="n">
-        <v>39.44241333007812</v>
+        <v>39.44242095947266</v>
       </c>
     </row>
     <row r="1309">
@@ -13525,7 +13525,7 @@
         </is>
       </c>
       <c r="B1311" t="n">
-        <v>38.87976837158203</v>
+        <v>38.8797721862793</v>
       </c>
     </row>
     <row r="1312">
@@ -13555,7 +13555,7 @@
         </is>
       </c>
       <c r="B1314" t="n">
-        <v>39.1944694519043</v>
+        <v>39.19446563720703</v>
       </c>
     </row>
     <row r="1315">
@@ -13565,7 +13565,7 @@
         </is>
       </c>
       <c r="B1315" t="n">
-        <v>39.24215316772461</v>
+        <v>39.24215698242188</v>
       </c>
     </row>
     <row r="1316">
@@ -13575,7 +13575,7 @@
         </is>
       </c>
       <c r="B1316" t="n">
-        <v>38.96560287475586</v>
+        <v>38.96559906005859</v>
       </c>
     </row>
     <row r="1317">
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="B1317" t="n">
-        <v>38.99420547485352</v>
+        <v>38.99420166015625</v>
       </c>
     </row>
     <row r="1318">
@@ -13595,7 +13595,7 @@
         </is>
       </c>
       <c r="B1318" t="n">
-        <v>38.96560287475586</v>
+        <v>38.96559906005859</v>
       </c>
     </row>
     <row r="1319">
@@ -13625,7 +13625,7 @@
         </is>
       </c>
       <c r="B1321" t="n">
-        <v>39.24215316772461</v>
+        <v>39.24215698242188</v>
       </c>
     </row>
     <row r="1322">
@@ -13645,7 +13645,7 @@
         </is>
       </c>
       <c r="B1323" t="n">
-        <v>39.39473342895508</v>
+        <v>39.39473724365234</v>
       </c>
     </row>
     <row r="1324">
@@ -13665,7 +13665,7 @@
         </is>
       </c>
       <c r="B1325" t="n">
-        <v>39.33752059936523</v>
+        <v>39.33751678466797</v>
       </c>
     </row>
     <row r="1326">
@@ -13685,7 +13685,7 @@
         </is>
       </c>
       <c r="B1327" t="n">
-        <v>39.86201095581055</v>
+        <v>39.86201858520508</v>
       </c>
     </row>
     <row r="1328">
@@ -13715,7 +13715,7 @@
         </is>
       </c>
       <c r="B1330" t="n">
-        <v>38.65089416503906</v>
+        <v>38.65089797973633</v>
       </c>
     </row>
     <row r="1331">
@@ -13725,7 +13725,7 @@
         </is>
       </c>
       <c r="B1331" t="n">
-        <v>38.40295791625977</v>
+        <v>38.40295028686523</v>
       </c>
     </row>
     <row r="1332">
@@ -13755,7 +13755,7 @@
         </is>
       </c>
       <c r="B1334" t="n">
-        <v>38.02149963378906</v>
+        <v>38.0214958190918</v>
       </c>
     </row>
     <row r="1335">
@@ -13795,7 +13795,7 @@
         </is>
       </c>
       <c r="B1338" t="n">
-        <v>38.72719192504883</v>
+        <v>38.72718811035156</v>
       </c>
     </row>
     <row r="1339">
@@ -13805,7 +13805,7 @@
         </is>
       </c>
       <c r="B1339" t="n">
-        <v>38.81301879882812</v>
+        <v>38.81301498413086</v>
       </c>
     </row>
     <row r="1340">
@@ -13835,7 +13835,7 @@
         </is>
       </c>
       <c r="B1342" t="n">
-        <v>39.08957290649414</v>
+        <v>39.08957672119141</v>
       </c>
     </row>
     <row r="1343">
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="B1347" t="n">
-        <v>40.31022644042969</v>
+        <v>40.31022262573242</v>
       </c>
     </row>
     <row r="1348">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="B1350" t="n">
-        <v>40.52956390380859</v>
+        <v>40.52956008911133</v>
       </c>
     </row>
     <row r="1351">
@@ -13935,7 +13935,7 @@
         </is>
       </c>
       <c r="B1352" t="n">
-        <v>41.0540657043457</v>
+        <v>41.05406188964844</v>
       </c>
     </row>
     <row r="1353">
@@ -13945,7 +13945,7 @@
         </is>
       </c>
       <c r="B1353" t="n">
-        <v>41.49273681640625</v>
+        <v>41.49273300170898</v>
       </c>
     </row>
     <row r="1354">
@@ -13955,7 +13955,7 @@
         </is>
       </c>
       <c r="B1354" t="n">
-        <v>41.57856369018555</v>
+        <v>41.57855987548828</v>
       </c>
     </row>
     <row r="1355">
@@ -13965,7 +13965,7 @@
         </is>
       </c>
       <c r="B1355" t="n">
-        <v>41.7597541809082</v>
+        <v>41.75975799560547</v>
       </c>
     </row>
     <row r="1356">
@@ -13995,7 +13995,7 @@
         </is>
       </c>
       <c r="B1358" t="n">
-        <v>41.21618270874023</v>
+        <v>41.2161865234375</v>
       </c>
     </row>
     <row r="1359">
@@ -14005,7 +14005,7 @@
         </is>
       </c>
       <c r="B1359" t="n">
-        <v>40.91101837158203</v>
+        <v>40.9110221862793</v>
       </c>
     </row>
     <row r="1360">
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="B1361" t="n">
-        <v>40.96823501586914</v>
+        <v>40.96823120117188</v>
       </c>
     </row>
     <row r="1362">
@@ -14035,7 +14035,7 @@
         </is>
       </c>
       <c r="B1362" t="n">
-        <v>40.35791015625</v>
+        <v>40.35791397094727</v>
       </c>
     </row>
     <row r="1363">
@@ -14045,7 +14045,7 @@
         </is>
       </c>
       <c r="B1363" t="n">
-        <v>40.24346923828125</v>
+        <v>40.24347305297852</v>
       </c>
     </row>
     <row r="1364">
@@ -14055,7 +14055,7 @@
         </is>
       </c>
       <c r="B1364" t="n">
-        <v>39.85248565673828</v>
+        <v>39.85247802734375</v>
       </c>
     </row>
     <row r="1365">
@@ -14065,7 +14065,7 @@
         </is>
       </c>
       <c r="B1365" t="n">
-        <v>40.27207946777344</v>
+        <v>40.2720832824707</v>
       </c>
     </row>
     <row r="1366">
@@ -14085,7 +14085,7 @@
         </is>
       </c>
       <c r="B1367" t="n">
-        <v>40.34837341308594</v>
+        <v>40.34836959838867</v>
       </c>
     </row>
     <row r="1368">
@@ -14095,7 +14095,7 @@
         </is>
       </c>
       <c r="B1368" t="n">
-        <v>40.54863739013672</v>
+        <v>40.54863357543945</v>
       </c>
     </row>
     <row r="1369">
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="B1369" t="n">
-        <v>40.09088897705078</v>
+        <v>40.09088516235352</v>
       </c>
     </row>
     <row r="1370">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="B1370" t="n">
-        <v>40.32929611206055</v>
+        <v>40.32929992675781</v>
       </c>
     </row>
     <row r="1371">
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="B1371" t="n">
-        <v>40.19486999511719</v>
+        <v>40.19486618041992</v>
       </c>
     </row>
     <row r="1372">
@@ -14135,7 +14135,7 @@
         </is>
       </c>
       <c r="B1372" t="n">
-        <v>40.5981559753418</v>
+        <v>40.59815979003906</v>
       </c>
     </row>
     <row r="1373">
@@ -14145,7 +14145,7 @@
         </is>
       </c>
       <c r="B1373" t="n">
-        <v>40.50213623046875</v>
+        <v>40.50214004516602</v>
       </c>
     </row>
     <row r="1374">
@@ -14155,7 +14155,7 @@
         </is>
       </c>
       <c r="B1374" t="n">
-        <v>40.55014801025391</v>
+        <v>40.55014419555664</v>
       </c>
     </row>
     <row r="1375">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="B1383" t="n">
-        <v>40.89582824707031</v>
+        <v>40.89583206176758</v>
       </c>
     </row>
     <row r="1384">
@@ -14275,7 +14275,7 @@
         </is>
       </c>
       <c r="B1386" t="n">
-        <v>41.72161865234375</v>
+        <v>41.72162246704102</v>
       </c>
     </row>
     <row r="1387">
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="B1387" t="n">
-        <v>41.89446258544922</v>
+        <v>41.89445877075195</v>
       </c>
     </row>
     <row r="1388">
@@ -14305,7 +14305,7 @@
         </is>
       </c>
       <c r="B1389" t="n">
-        <v>42.07690048217773</v>
+        <v>42.076904296875</v>
       </c>
     </row>
     <row r="1390">
@@ -14345,7 +14345,7 @@
         </is>
       </c>
       <c r="B1393" t="n">
-        <v>42.28815078735352</v>
+        <v>42.28814697265625</v>
       </c>
     </row>
     <row r="1394">
@@ -14365,7 +14365,7 @@
         </is>
       </c>
       <c r="B1395" t="n">
-        <v>41.83684921264648</v>
+        <v>41.83684539794922</v>
       </c>
     </row>
     <row r="1396">
@@ -14375,7 +14375,7 @@
         </is>
       </c>
       <c r="B1396" t="n">
-        <v>41.44315719604492</v>
+        <v>41.44315338134766</v>
       </c>
     </row>
     <row r="1397">
@@ -14395,7 +14395,7 @@
         </is>
       </c>
       <c r="B1398" t="n">
-        <v>41.38554000854492</v>
+        <v>41.38553619384766</v>
       </c>
     </row>
     <row r="1399">
@@ -14405,7 +14405,7 @@
         </is>
       </c>
       <c r="B1399" t="n">
-        <v>41.02066040039062</v>
+        <v>41.02065658569336</v>
       </c>
     </row>
     <row r="1400">
@@ -14415,7 +14415,7 @@
         </is>
       </c>
       <c r="B1400" t="n">
-        <v>40.42531585693359</v>
+        <v>40.42531967163086</v>
       </c>
     </row>
     <row r="1401">
@@ -14475,7 +14475,7 @@
         </is>
       </c>
       <c r="B1406" t="n">
-        <v>40.52133941650391</v>
+        <v>40.52134323120117</v>
       </c>
     </row>
     <row r="1407">
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="B1413" t="n">
-        <v>40.52133941650391</v>
+        <v>40.52134323120117</v>
       </c>
     </row>
     <row r="1414">
@@ -14565,7 +14565,7 @@
         </is>
       </c>
       <c r="B1415" t="n">
-        <v>40.75179672241211</v>
+        <v>40.75179290771484</v>
       </c>
     </row>
     <row r="1416">
@@ -14655,7 +14655,7 @@
         </is>
       </c>
       <c r="B1424" t="n">
-        <v>41.79843521118164</v>
+        <v>41.79843902587891</v>
       </c>
     </row>
     <row r="1425">
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="B1425" t="n">
-        <v>41.5391731262207</v>
+        <v>41.53917694091797</v>
       </c>
     </row>
     <row r="1426">
@@ -14685,7 +14685,7 @@
         </is>
       </c>
       <c r="B1427" t="n">
-        <v>41.64479827880859</v>
+        <v>41.64480209350586</v>
       </c>
     </row>
     <row r="1428">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="B1431" t="n">
-        <v>40.11804962158203</v>
+        <v>40.11804580688477</v>
       </c>
     </row>
     <row r="1432">
@@ -14735,7 +14735,7 @@
         </is>
       </c>
       <c r="B1432" t="n">
-        <v>40.45412826538086</v>
+        <v>40.45413208007812</v>
       </c>
     </row>
     <row r="1433">
@@ -14745,7 +14745,7 @@
         </is>
       </c>
       <c r="B1433" t="n">
-        <v>40.30049514770508</v>
+        <v>40.30049133300781</v>
       </c>
     </row>
     <row r="1434">
@@ -14755,7 +14755,7 @@
         </is>
       </c>
       <c r="B1434" t="n">
-        <v>40.5981559753418</v>
+        <v>40.59815979003906</v>
       </c>
     </row>
     <row r="1435">
@@ -14765,7 +14765,7 @@
         </is>
       </c>
       <c r="B1435" t="n">
-        <v>40.93423843383789</v>
+        <v>40.93424224853516</v>
       </c>
     </row>
     <row r="1436">
@@ -14815,7 +14815,7 @@
         </is>
       </c>
       <c r="B1440" t="n">
-        <v>42.03849029541016</v>
+        <v>42.03849411010742</v>
       </c>
     </row>
     <row r="1441">
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="B1441" t="n">
-        <v>41.95207214355469</v>
+        <v>41.95206832885742</v>
       </c>
     </row>
     <row r="1442">
@@ -14835,7 +14835,7 @@
         </is>
       </c>
       <c r="B1442" t="n">
-        <v>42.27854919433594</v>
+        <v>42.27854537963867</v>
       </c>
     </row>
     <row r="1443">
@@ -14855,7 +14855,7 @@
         </is>
       </c>
       <c r="B1444" t="n">
-        <v>43.25797271728516</v>
+        <v>43.25796890258789</v>
       </c>
     </row>
     <row r="1445">
@@ -14865,7 +14865,7 @@
         </is>
       </c>
       <c r="B1445" t="n">
-        <v>44.84233856201172</v>
+        <v>44.84233474731445</v>
       </c>
     </row>
     <row r="1446">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="B1449" t="n">
-        <v>45.22642517089844</v>
+        <v>45.2264289855957</v>
       </c>
     </row>
     <row r="1450">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="B1455" t="n">
-        <v>44.19898986816406</v>
+        <v>44.1989860534668</v>
       </c>
     </row>
     <row r="1456">
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="B1459" t="n">
-        <v>43.72848510742188</v>
+        <v>43.72848129272461</v>
       </c>
     </row>
     <row r="1460">
@@ -15015,7 +15015,7 @@
         </is>
       </c>
       <c r="B1460" t="n">
-        <v>43.6612663269043</v>
+        <v>43.66127014160156</v>
       </c>
     </row>
     <row r="1461">
@@ -15025,7 +15025,7 @@
         </is>
       </c>
       <c r="B1461" t="n">
-        <v>44.09336471557617</v>
+        <v>44.09336090087891</v>
       </c>
     </row>
     <row r="1462">
@@ -15055,7 +15055,7 @@
         </is>
       </c>
       <c r="B1464" t="n">
-        <v>43.43080902099609</v>
+        <v>43.43081283569336</v>
       </c>
     </row>
     <row r="1465">
@@ -15065,7 +15065,7 @@
         </is>
       </c>
       <c r="B1465" t="n">
-        <v>43.36360168457031</v>
+        <v>43.36359786987305</v>
       </c>
     </row>
     <row r="1466">
@@ -15085,7 +15085,7 @@
         </is>
       </c>
       <c r="B1467" t="n">
-        <v>43.51723098754883</v>
+        <v>43.51723480224609</v>
       </c>
     </row>
     <row r="1468">
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="B1468" t="n">
-        <v>43.3828010559082</v>
+        <v>43.38280487060547</v>
       </c>
     </row>
     <row r="1469">
@@ -15125,7 +15125,7 @@
         </is>
       </c>
       <c r="B1471" t="n">
-        <v>42.72025299072266</v>
+        <v>42.72024917602539</v>
       </c>
     </row>
     <row r="1472">
@@ -15145,7 +15145,7 @@
         </is>
       </c>
       <c r="B1473" t="n">
-        <v>43.54603958129883</v>
+        <v>43.54603576660156</v>
       </c>
     </row>
     <row r="1474">
@@ -15165,7 +15165,7 @@
         </is>
       </c>
       <c r="B1475" t="n">
-        <v>43.95893096923828</v>
+        <v>43.95893478393555</v>
       </c>
     </row>
     <row r="1476">
@@ -15185,7 +15185,7 @@
         </is>
       </c>
       <c r="B1477" t="n">
-        <v>42.54740905761719</v>
+        <v>42.54741287231445</v>
       </c>
     </row>
     <row r="1478">
@@ -15315,7 +15315,7 @@
         </is>
       </c>
       <c r="B1490" t="n">
-        <v>41.5391731262207</v>
+        <v>41.53917694091797</v>
       </c>
     </row>
     <row r="1491">
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="B1492" t="n">
-        <v>41.78883361816406</v>
+        <v>41.78883743286133</v>
       </c>
     </row>
     <row r="1493">
@@ -15345,7 +15345,7 @@
         </is>
       </c>
       <c r="B1493" t="n">
-        <v>41.89446258544922</v>
+        <v>41.89445877075195</v>
       </c>
     </row>
     <row r="1494">
@@ -15385,7 +15385,7 @@
         </is>
       </c>
       <c r="B1497" t="n">
-        <v>42.27854919433594</v>
+        <v>42.27854537963867</v>
       </c>
     </row>
     <row r="1498">
@@ -15415,7 +15415,7 @@
         </is>
       </c>
       <c r="B1500" t="n">
-        <v>42.27854919433594</v>
+        <v>42.27854537963867</v>
       </c>
     </row>
     <row r="1501">
